--- a/pdfs/caminhao-basculante-rev02-user.xlsx
+++ b/pdfs/caminhao-basculante-rev02-user.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jdemitocombr-my.sharepoint.com/personal/dewid_dias_jdemito_com_br/Documents/Documents/Curso de Power BI/Documentos Dewid/TCC + ESTÁGIO/Atualização dos Checklist/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6a1be6d7d730111a/Desktop/check/check/pdfs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="209" documentId="8_{2FB653C5-A0C9-48FB-8A03-789A1D875FD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1EA17386-6096-4C83-9531-1E3E96627DC2}"/>
+  <xr:revisionPtr revIDLastSave="216" documentId="8_{2FB653C5-A0C9-48FB-8A03-789A1D875FD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0585617F-5434-46C0-92BE-6874F05BDE54}"/>
   <bookViews>
-    <workbookView xWindow="-4185" yWindow="-16320" windowWidth="29040" windowHeight="15840" tabRatio="910" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="910" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CAMINHÃO BASCULANTE" sheetId="75" r:id="rId1"/>
@@ -693,7 +693,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="138">
+  <cellXfs count="139">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -743,37 +743,292 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -784,309 +1039,65 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1318,7 +1329,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="6130739" y="4078942"/>
+          <a:off x="6119533" y="4074868"/>
           <a:ext cx="346262" cy="245968"/>
           <a:chOff x="5939119" y="5076266"/>
           <a:chExt cx="334745" cy="291352"/>
@@ -1470,7 +1481,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="9534525" y="5629835"/>
+          <a:off x="9517207" y="5649191"/>
           <a:ext cx="257175" cy="228600"/>
           <a:chOff x="5939119" y="5076266"/>
           <a:chExt cx="334745" cy="291352"/>
@@ -1622,7 +1633,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="9534525" y="5921188"/>
+          <a:off x="9517207" y="5943600"/>
           <a:ext cx="257175" cy="228600"/>
           <a:chOff x="5939119" y="5076266"/>
           <a:chExt cx="334745" cy="291352"/>
@@ -1774,7 +1785,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="9534525" y="7895104"/>
+          <a:off x="9517207" y="7942984"/>
           <a:ext cx="257175" cy="228600"/>
           <a:chOff x="5939119" y="5076266"/>
           <a:chExt cx="334745" cy="291352"/>
@@ -1926,7 +1937,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="9544050" y="8477810"/>
+          <a:off x="9526732" y="8531802"/>
           <a:ext cx="257175" cy="228600"/>
           <a:chOff x="5939119" y="5076266"/>
           <a:chExt cx="334745" cy="291352"/>
@@ -2078,7 +2089,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="9561739" y="7368428"/>
+          <a:off x="9544421" y="7406120"/>
           <a:ext cx="257175" cy="228600"/>
           <a:chOff x="5939119" y="5076266"/>
           <a:chExt cx="334745" cy="291352"/>
@@ -2230,7 +2241,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="9547412" y="6196852"/>
+          <a:off x="9530094" y="6222320"/>
           <a:ext cx="257175" cy="228600"/>
           <a:chOff x="5939119" y="5076266"/>
           <a:chExt cx="334745" cy="291352"/>
@@ -2382,7 +2393,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="9553575" y="8176932"/>
+          <a:off x="9536257" y="8227868"/>
           <a:ext cx="257175" cy="228600"/>
           <a:chOff x="5939119" y="5076266"/>
           <a:chExt cx="334745" cy="291352"/>
@@ -2534,7 +2545,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="9547411" y="6499411"/>
+          <a:off x="9530093" y="6527935"/>
           <a:ext cx="257175" cy="228600"/>
           <a:chOff x="5939119" y="5076266"/>
           <a:chExt cx="334745" cy="291352"/>
@@ -2686,7 +2697,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="9536206" y="13872883"/>
+          <a:off x="9518888" y="13980867"/>
           <a:ext cx="257175" cy="228600"/>
           <a:chOff x="5939119" y="5076266"/>
           <a:chExt cx="334745" cy="291352"/>
@@ -2928,8 +2939,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="7194176" y="23767677"/>
-          <a:ext cx="391646" cy="228600"/>
+          <a:off x="7186026" y="23892979"/>
+          <a:ext cx="385534" cy="228600"/>
           <a:chOff x="5939119" y="5076266"/>
           <a:chExt cx="334745" cy="291352"/>
         </a:xfrm>
@@ -3125,7 +3136,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="9547412" y="23207383"/>
+          <a:off x="9530094" y="23326573"/>
           <a:ext cx="257175" cy="228600"/>
           <a:chOff x="5939119" y="5076266"/>
           <a:chExt cx="334745" cy="291352"/>
@@ -3321,7 +3332,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="9547411" y="6790764"/>
+          <a:off x="9530093" y="6822344"/>
           <a:ext cx="257175" cy="228600"/>
           <a:chOff x="5939119" y="5076266"/>
           <a:chExt cx="334745" cy="291352"/>
@@ -3473,7 +3484,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="9547411" y="7082117"/>
+          <a:off x="9530093" y="7116753"/>
           <a:ext cx="257175" cy="228600"/>
           <a:chOff x="5939119" y="5076266"/>
           <a:chExt cx="334745" cy="291352"/>
@@ -3670,7 +3681,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="9544050" y="10225928"/>
+          <a:off x="9526732" y="10298257"/>
           <a:ext cx="257175" cy="228600"/>
           <a:chOff x="5939119" y="5076266"/>
           <a:chExt cx="334745" cy="291352"/>
@@ -3867,7 +3878,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="9536206" y="12785912"/>
+          <a:off x="9518888" y="12889821"/>
           <a:ext cx="257175" cy="228600"/>
           <a:chOff x="5939119" y="5076266"/>
           <a:chExt cx="334745" cy="291352"/>
@@ -4019,7 +4030,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="9558618" y="20069735"/>
+          <a:off x="9541300" y="20191981"/>
           <a:ext cx="257175" cy="228600"/>
           <a:chOff x="5939119" y="5076266"/>
           <a:chExt cx="334745" cy="291352"/>
@@ -4171,7 +4182,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="9547411" y="21459264"/>
+          <a:off x="9530093" y="21572341"/>
           <a:ext cx="257175" cy="228600"/>
           <a:chOff x="5939119" y="5076266"/>
           <a:chExt cx="334745" cy="291352"/>
@@ -4368,7 +4379,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="9536206" y="12203206"/>
+          <a:off x="9518888" y="12301003"/>
           <a:ext cx="257175" cy="228600"/>
           <a:chOff x="5939119" y="5076266"/>
           <a:chExt cx="334745" cy="291352"/>
@@ -4520,7 +4531,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="9536206" y="12494559"/>
+          <a:off x="9518888" y="12595412"/>
           <a:ext cx="257175" cy="228600"/>
           <a:chOff x="5939119" y="5076266"/>
           <a:chExt cx="334745" cy="291352"/>
@@ -4672,7 +4683,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="9536206" y="13581530"/>
+          <a:off x="9518888" y="13686457"/>
           <a:ext cx="257175" cy="228600"/>
           <a:chOff x="5939119" y="5076266"/>
           <a:chExt cx="334745" cy="291352"/>
@@ -4824,7 +4835,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="9536206" y="14141824"/>
+          <a:off x="9518888" y="14240639"/>
           <a:ext cx="257175" cy="228600"/>
           <a:chOff x="5939119" y="5076266"/>
           <a:chExt cx="334745" cy="291352"/>
@@ -5066,7 +5077,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="9536206" y="15542559"/>
+          <a:off x="9518888" y="15660730"/>
           <a:ext cx="257175" cy="228600"/>
           <a:chOff x="5939119" y="5076266"/>
           <a:chExt cx="334745" cy="291352"/>
@@ -5308,7 +5319,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="9536206" y="17290677"/>
+          <a:off x="9518888" y="17427185"/>
           <a:ext cx="257175" cy="228600"/>
           <a:chOff x="5939119" y="5076266"/>
           <a:chExt cx="334745" cy="291352"/>
@@ -5460,7 +5471,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="9558618" y="18971558"/>
+          <a:off x="9541300" y="19118253"/>
           <a:ext cx="257175" cy="228600"/>
           <a:chOff x="5939119" y="5076266"/>
           <a:chExt cx="334745" cy="291352"/>
@@ -5612,7 +5623,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="9544050" y="11682693"/>
+          <a:off x="9526732" y="11770302"/>
           <a:ext cx="257175" cy="228600"/>
           <a:chOff x="5939119" y="5076266"/>
           <a:chExt cx="334745" cy="291352"/>
@@ -5899,7 +5910,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="9544050" y="11099987"/>
+          <a:off x="9526732" y="11181484"/>
           <a:ext cx="257175" cy="228600"/>
           <a:chOff x="5939119" y="5076266"/>
           <a:chExt cx="334745" cy="291352"/>
@@ -6101,7 +6112,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="9569824" y="9356911"/>
+          <a:off x="9552506" y="9420072"/>
           <a:ext cx="257175" cy="228600"/>
           <a:chOff x="5939119" y="5076266"/>
           <a:chExt cx="334745" cy="291352"/>
@@ -6604,235 +6615,235 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="75.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="55"/>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="57" t="s">
+      <c r="A1" s="113"/>
+      <c r="B1" s="114"/>
+      <c r="C1" s="114"/>
+      <c r="D1" s="115" t="s">
         <v>80</v>
       </c>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
-      <c r="G1" s="57"/>
-      <c r="H1" s="57"/>
-      <c r="I1" s="57"/>
-      <c r="J1" s="57"/>
-      <c r="K1" s="57"/>
-      <c r="L1" s="57"/>
-      <c r="M1" s="58" t="e" vm="1">
+      <c r="E1" s="115"/>
+      <c r="F1" s="115"/>
+      <c r="G1" s="115"/>
+      <c r="H1" s="115"/>
+      <c r="I1" s="115"/>
+      <c r="J1" s="115"/>
+      <c r="K1" s="115"/>
+      <c r="L1" s="115"/>
+      <c r="M1" s="82" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="N1" s="59"/>
+      <c r="N1" s="83"/>
     </row>
     <row r="2" spans="1:16" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="43" t="s">
+      <c r="A2" s="101" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="46" t="s">
+      <c r="B2" s="102"/>
+      <c r="C2" s="102"/>
+      <c r="D2" s="103"/>
+      <c r="E2" s="104" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="47"/>
-      <c r="G2" s="45"/>
-      <c r="H2" s="47" t="s">
+      <c r="F2" s="105"/>
+      <c r="G2" s="103"/>
+      <c r="H2" s="105" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="47"/>
-      <c r="J2" s="47"/>
-      <c r="K2" s="47"/>
-      <c r="L2" s="46" t="s">
+      <c r="I2" s="105"/>
+      <c r="J2" s="105"/>
+      <c r="K2" s="105"/>
+      <c r="L2" s="104" t="s">
         <v>96</v>
       </c>
-      <c r="M2" s="44"/>
-      <c r="N2" s="48"/>
+      <c r="M2" s="102"/>
+      <c r="N2" s="106"/>
       <c r="O2" s="15"/>
       <c r="P2" s="16"/>
     </row>
     <row r="3" spans="1:16" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="49" t="s">
+      <c r="A3" s="107" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="50"/>
-      <c r="C3" s="50"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="49" t="s">
+      <c r="B3" s="108"/>
+      <c r="C3" s="108"/>
+      <c r="D3" s="109"/>
+      <c r="E3" s="107" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="50"/>
-      <c r="G3" s="50"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="52" t="s">
+      <c r="F3" s="108"/>
+      <c r="G3" s="108"/>
+      <c r="H3" s="109"/>
+      <c r="I3" s="110" t="s">
         <v>5</v>
       </c>
-      <c r="J3" s="53"/>
-      <c r="K3" s="53"/>
-      <c r="L3" s="53"/>
-      <c r="M3" s="53"/>
-      <c r="N3" s="54"/>
+      <c r="J3" s="111"/>
+      <c r="K3" s="111"/>
+      <c r="L3" s="111"/>
+      <c r="M3" s="111"/>
+      <c r="N3" s="112"/>
       <c r="O3" s="15"/>
       <c r="P3" s="16"/>
     </row>
     <row r="4" spans="1:16" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="60" t="s">
+      <c r="A4" s="95" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="61"/>
-      <c r="C4" s="61"/>
-      <c r="D4" s="62"/>
-      <c r="E4" s="60" t="s">
+      <c r="B4" s="96"/>
+      <c r="C4" s="96"/>
+      <c r="D4" s="97"/>
+      <c r="E4" s="95" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="61"/>
-      <c r="G4" s="61"/>
-      <c r="H4" s="62"/>
-      <c r="I4" s="60" t="s">
+      <c r="F4" s="96"/>
+      <c r="G4" s="96"/>
+      <c r="H4" s="97"/>
+      <c r="I4" s="95" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="61"/>
-      <c r="K4" s="61"/>
-      <c r="L4" s="61"/>
-      <c r="M4" s="61"/>
-      <c r="N4" s="62"/>
+      <c r="J4" s="96"/>
+      <c r="K4" s="96"/>
+      <c r="L4" s="96"/>
+      <c r="M4" s="96"/>
+      <c r="N4" s="97"/>
     </row>
     <row r="5" spans="1:16" s="8" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="63" t="s">
+      <c r="A5" s="98" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="64"/>
-      <c r="C5" s="64"/>
-      <c r="D5" s="65"/>
-      <c r="E5" s="63" t="s">
+      <c r="B5" s="99"/>
+      <c r="C5" s="99"/>
+      <c r="D5" s="100"/>
+      <c r="E5" s="98" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="64"/>
-      <c r="G5" s="64"/>
-      <c r="H5" s="65"/>
-      <c r="I5" s="60" t="s">
+      <c r="F5" s="99"/>
+      <c r="G5" s="99"/>
+      <c r="H5" s="100"/>
+      <c r="I5" s="95" t="s">
         <v>7</v>
       </c>
-      <c r="J5" s="61"/>
-      <c r="K5" s="61"/>
-      <c r="L5" s="61"/>
-      <c r="M5" s="61"/>
-      <c r="N5" s="62"/>
+      <c r="J5" s="96"/>
+      <c r="K5" s="96"/>
+      <c r="L5" s="96"/>
+      <c r="M5" s="96"/>
+      <c r="N5" s="97"/>
     </row>
     <row r="6" spans="1:16" s="8" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="60" t="s">
+      <c r="A6" s="95" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="61"/>
-      <c r="C6" s="61"/>
-      <c r="D6" s="62"/>
-      <c r="E6" s="60" t="s">
+      <c r="B6" s="96"/>
+      <c r="C6" s="96"/>
+      <c r="D6" s="97"/>
+      <c r="E6" s="95" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="61"/>
-      <c r="G6" s="61"/>
-      <c r="H6" s="62"/>
-      <c r="I6" s="60" t="s">
+      <c r="F6" s="96"/>
+      <c r="G6" s="96"/>
+      <c r="H6" s="97"/>
+      <c r="I6" s="95" t="s">
         <v>8</v>
       </c>
-      <c r="J6" s="61"/>
-      <c r="K6" s="61"/>
-      <c r="L6" s="61"/>
-      <c r="M6" s="61"/>
-      <c r="N6" s="62"/>
+      <c r="J6" s="96"/>
+      <c r="K6" s="96"/>
+      <c r="L6" s="96"/>
+      <c r="M6" s="96"/>
+      <c r="N6" s="97"/>
     </row>
     <row r="7" spans="1:16" s="8" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="60" t="s">
+      <c r="A7" s="95" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="61"/>
-      <c r="C7" s="61"/>
-      <c r="D7" s="62"/>
-      <c r="E7" s="60" t="s">
+      <c r="B7" s="96"/>
+      <c r="C7" s="96"/>
+      <c r="D7" s="97"/>
+      <c r="E7" s="95" t="s">
         <v>9</v>
       </c>
-      <c r="F7" s="61"/>
-      <c r="G7" s="61"/>
-      <c r="H7" s="62"/>
-      <c r="I7" s="60" t="s">
+      <c r="F7" s="96"/>
+      <c r="G7" s="96"/>
+      <c r="H7" s="97"/>
+      <c r="I7" s="95" t="s">
         <v>9</v>
       </c>
-      <c r="J7" s="61"/>
-      <c r="K7" s="61"/>
-      <c r="L7" s="61"/>
-      <c r="M7" s="61"/>
-      <c r="N7" s="62"/>
+      <c r="J7" s="96"/>
+      <c r="K7" s="96"/>
+      <c r="L7" s="96"/>
+      <c r="M7" s="96"/>
+      <c r="N7" s="97"/>
     </row>
     <row r="8" spans="1:16" s="8" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="60" t="s">
+      <c r="A8" s="95" t="s">
         <v>101</v>
       </c>
-      <c r="B8" s="61"/>
-      <c r="C8" s="61"/>
-      <c r="D8" s="62"/>
-      <c r="E8" s="60" t="s">
+      <c r="B8" s="96"/>
+      <c r="C8" s="96"/>
+      <c r="D8" s="97"/>
+      <c r="E8" s="95" t="s">
         <v>101</v>
       </c>
-      <c r="F8" s="61"/>
-      <c r="G8" s="61"/>
-      <c r="H8" s="62"/>
-      <c r="I8" s="60" t="s">
+      <c r="F8" s="96"/>
+      <c r="G8" s="96"/>
+      <c r="H8" s="97"/>
+      <c r="I8" s="95" t="s">
         <v>101</v>
       </c>
-      <c r="J8" s="61"/>
-      <c r="K8" s="61"/>
-      <c r="L8" s="61"/>
-      <c r="M8" s="61"/>
-      <c r="N8" s="62"/>
+      <c r="J8" s="96"/>
+      <c r="K8" s="96"/>
+      <c r="L8" s="96"/>
+      <c r="M8" s="96"/>
+      <c r="N8" s="97"/>
     </row>
     <row r="9" spans="1:16" ht="41.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="67" t="s">
+      <c r="A9" s="81" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="58"/>
-      <c r="C9" s="58"/>
-      <c r="D9" s="58"/>
-      <c r="E9" s="58"/>
-      <c r="F9" s="58"/>
-      <c r="G9" s="58"/>
-      <c r="H9" s="58"/>
-      <c r="I9" s="58"/>
-      <c r="J9" s="58"/>
-      <c r="K9" s="58"/>
-      <c r="L9" s="58"/>
-      <c r="M9" s="58"/>
-      <c r="N9" s="59"/>
+      <c r="B9" s="82"/>
+      <c r="C9" s="82"/>
+      <c r="D9" s="82"/>
+      <c r="E9" s="82"/>
+      <c r="F9" s="82"/>
+      <c r="G9" s="82"/>
+      <c r="H9" s="82"/>
+      <c r="I9" s="82"/>
+      <c r="J9" s="82"/>
+      <c r="K9" s="82"/>
+      <c r="L9" s="82"/>
+      <c r="M9" s="82"/>
+      <c r="N9" s="83"/>
     </row>
     <row r="10" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="68" t="s">
+      <c r="A10" s="84" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="69"/>
-      <c r="C10" s="69"/>
-      <c r="D10" s="69"/>
-      <c r="E10" s="69"/>
-      <c r="F10" s="69"/>
-      <c r="G10" s="69"/>
+      <c r="B10" s="85"/>
+      <c r="C10" s="85"/>
+      <c r="D10" s="85"/>
+      <c r="E10" s="85"/>
+      <c r="F10" s="85"/>
+      <c r="G10" s="85"/>
       <c r="H10" s="10"/>
-      <c r="I10" s="70" t="s">
+      <c r="I10" s="86" t="s">
         <v>12</v>
       </c>
-      <c r="J10" s="70"/>
-      <c r="K10" s="70"/>
-      <c r="L10" s="70"/>
-      <c r="M10" s="70"/>
-      <c r="N10" s="71"/>
+      <c r="J10" s="86"/>
+      <c r="K10" s="86"/>
+      <c r="L10" s="86"/>
+      <c r="M10" s="86"/>
+      <c r="N10" s="87"/>
     </row>
     <row r="11" spans="1:16" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="72" t="s">
+      <c r="A11" s="88" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="73"/>
-      <c r="C11" s="73"/>
-      <c r="D11" s="73"/>
-      <c r="E11" s="73"/>
-      <c r="F11" s="73"/>
-      <c r="G11" s="73"/>
-      <c r="H11" s="73"/>
-      <c r="I11" s="74"/>
+      <c r="B11" s="89"/>
+      <c r="C11" s="89"/>
+      <c r="D11" s="89"/>
+      <c r="E11" s="89"/>
+      <c r="F11" s="89"/>
+      <c r="G11" s="89"/>
+      <c r="H11" s="89"/>
+      <c r="I11" s="90"/>
       <c r="J11" s="12" t="s">
         <v>14</v>
       </c>
@@ -6842,1708 +6853,1708 @@
       <c r="L11" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="M11" s="75" t="s">
+      <c r="M11" s="91" t="s">
         <v>17</v>
       </c>
-      <c r="N11" s="76"/>
+      <c r="N11" s="92"/>
     </row>
     <row r="12" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="77" t="s">
+      <c r="A12" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="78"/>
-      <c r="C12" s="78"/>
-      <c r="D12" s="78"/>
-      <c r="E12" s="78"/>
-      <c r="F12" s="78"/>
-      <c r="G12" s="78"/>
-      <c r="H12" s="78"/>
-      <c r="I12" s="78"/>
-      <c r="J12" s="78"/>
-      <c r="K12" s="78"/>
-      <c r="L12" s="78"/>
-      <c r="M12" s="79"/>
-      <c r="N12" s="80"/>
-    </row>
-    <row r="13" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="24"/>
+      <c r="C12" s="24"/>
+      <c r="D12" s="24"/>
+      <c r="E12" s="24"/>
+      <c r="F12" s="24"/>
+      <c r="G12" s="24"/>
+      <c r="H12" s="24"/>
+      <c r="I12" s="24"/>
+      <c r="J12" s="24"/>
+      <c r="K12" s="24"/>
+      <c r="L12" s="24"/>
+      <c r="M12" s="93"/>
+      <c r="N12" s="94"/>
+    </row>
+    <row r="13" spans="1:16" s="123" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <v>1</v>
       </c>
-      <c r="B13" s="66" t="s">
+      <c r="B13" s="80" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="24"/>
-      <c r="D13" s="24"/>
-      <c r="E13" s="24"/>
-      <c r="F13" s="24"/>
-      <c r="G13" s="24"/>
-      <c r="H13" s="24"/>
-      <c r="I13" s="25"/>
+      <c r="C13" s="73"/>
+      <c r="D13" s="73"/>
+      <c r="E13" s="73"/>
+      <c r="F13" s="73"/>
+      <c r="G13" s="73"/>
+      <c r="H13" s="73"/>
+      <c r="I13" s="74"/>
       <c r="J13" s="4"/>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
-      <c r="M13" s="26"/>
-      <c r="N13" s="27"/>
-    </row>
-    <row r="14" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M13" s="132"/>
+      <c r="N13" s="133"/>
+    </row>
+    <row r="14" spans="1:16" s="123" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>2</v>
       </c>
-      <c r="B14" s="66" t="s">
+      <c r="B14" s="80" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="24"/>
-      <c r="D14" s="24"/>
-      <c r="E14" s="24"/>
-      <c r="F14" s="24"/>
-      <c r="G14" s="24"/>
-      <c r="H14" s="24"/>
-      <c r="I14" s="25"/>
+      <c r="C14" s="73"/>
+      <c r="D14" s="73"/>
+      <c r="E14" s="73"/>
+      <c r="F14" s="73"/>
+      <c r="G14" s="73"/>
+      <c r="H14" s="73"/>
+      <c r="I14" s="74"/>
       <c r="J14" s="4"/>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
-      <c r="M14" s="26"/>
-      <c r="N14" s="27"/>
-    </row>
-    <row r="15" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M14" s="132"/>
+      <c r="N14" s="133"/>
+    </row>
+    <row r="15" spans="1:16" s="123" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>3</v>
       </c>
-      <c r="B15" s="81" t="s">
+      <c r="B15" s="79" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="37"/>
-      <c r="D15" s="37"/>
-      <c r="E15" s="37"/>
-      <c r="F15" s="37"/>
-      <c r="G15" s="37"/>
-      <c r="H15" s="37"/>
-      <c r="I15" s="38"/>
+      <c r="C15" s="124"/>
+      <c r="D15" s="124"/>
+      <c r="E15" s="124"/>
+      <c r="F15" s="124"/>
+      <c r="G15" s="124"/>
+      <c r="H15" s="124"/>
+      <c r="I15" s="125"/>
       <c r="J15" s="4"/>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
-      <c r="M15" s="26"/>
-      <c r="N15" s="27"/>
-    </row>
-    <row r="16" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M15" s="132"/>
+      <c r="N15" s="133"/>
+    </row>
+    <row r="16" spans="1:16" s="123" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>4</v>
       </c>
-      <c r="B16" s="81" t="s">
+      <c r="B16" s="79" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="37"/>
-      <c r="D16" s="37"/>
-      <c r="E16" s="37"/>
-      <c r="F16" s="37"/>
-      <c r="G16" s="37"/>
-      <c r="H16" s="37"/>
-      <c r="I16" s="38"/>
+      <c r="C16" s="124"/>
+      <c r="D16" s="124"/>
+      <c r="E16" s="124"/>
+      <c r="F16" s="124"/>
+      <c r="G16" s="124"/>
+      <c r="H16" s="124"/>
+      <c r="I16" s="125"/>
       <c r="J16" s="4"/>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
-      <c r="M16" s="26"/>
-      <c r="N16" s="27"/>
-    </row>
-    <row r="17" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M16" s="132"/>
+      <c r="N16" s="133"/>
+    </row>
+    <row r="17" spans="1:14" s="123" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
         <v>5</v>
       </c>
-      <c r="B17" s="81" t="s">
+      <c r="B17" s="79" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="37"/>
-      <c r="D17" s="37"/>
-      <c r="E17" s="37"/>
-      <c r="F17" s="37"/>
-      <c r="G17" s="37"/>
-      <c r="H17" s="37"/>
-      <c r="I17" s="38"/>
+      <c r="C17" s="124"/>
+      <c r="D17" s="124"/>
+      <c r="E17" s="124"/>
+      <c r="F17" s="124"/>
+      <c r="G17" s="124"/>
+      <c r="H17" s="124"/>
+      <c r="I17" s="125"/>
       <c r="J17" s="4"/>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
-      <c r="M17" s="26"/>
-      <c r="N17" s="27"/>
-    </row>
-    <row r="18" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M17" s="132"/>
+      <c r="N17" s="133"/>
+    </row>
+    <row r="18" spans="1:14" s="123" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
         <v>6</v>
       </c>
-      <c r="B18" s="81" t="s">
+      <c r="B18" s="79" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="37"/>
-      <c r="D18" s="37"/>
-      <c r="E18" s="37"/>
-      <c r="F18" s="37"/>
-      <c r="G18" s="37"/>
-      <c r="H18" s="37"/>
-      <c r="I18" s="38"/>
+      <c r="C18" s="124"/>
+      <c r="D18" s="124"/>
+      <c r="E18" s="124"/>
+      <c r="F18" s="124"/>
+      <c r="G18" s="124"/>
+      <c r="H18" s="124"/>
+      <c r="I18" s="125"/>
       <c r="J18" s="4"/>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
-      <c r="M18" s="26"/>
-      <c r="N18" s="27"/>
-    </row>
-    <row r="19" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M18" s="132"/>
+      <c r="N18" s="133"/>
+    </row>
+    <row r="19" spans="1:14" s="123" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
         <v>7</v>
       </c>
-      <c r="B19" s="81" t="s">
+      <c r="B19" s="79" t="s">
         <v>26</v>
       </c>
-      <c r="C19" s="37"/>
-      <c r="D19" s="37"/>
-      <c r="E19" s="37"/>
-      <c r="F19" s="37"/>
-      <c r="G19" s="37"/>
-      <c r="H19" s="37"/>
-      <c r="I19" s="38"/>
+      <c r="C19" s="124"/>
+      <c r="D19" s="124"/>
+      <c r="E19" s="124"/>
+      <c r="F19" s="124"/>
+      <c r="G19" s="124"/>
+      <c r="H19" s="124"/>
+      <c r="I19" s="125"/>
       <c r="J19" s="4"/>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
-      <c r="M19" s="26"/>
-      <c r="N19" s="27"/>
-    </row>
-    <row r="20" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M19" s="132"/>
+      <c r="N19" s="133"/>
+    </row>
+    <row r="20" spans="1:14" s="123" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
         <v>8</v>
       </c>
-      <c r="B20" s="81" t="s">
+      <c r="B20" s="79" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="37"/>
-      <c r="D20" s="37"/>
-      <c r="E20" s="37"/>
-      <c r="F20" s="37"/>
-      <c r="G20" s="37"/>
-      <c r="H20" s="37"/>
-      <c r="I20" s="38"/>
+      <c r="C20" s="124"/>
+      <c r="D20" s="124"/>
+      <c r="E20" s="124"/>
+      <c r="F20" s="124"/>
+      <c r="G20" s="124"/>
+      <c r="H20" s="124"/>
+      <c r="I20" s="125"/>
       <c r="J20" s="4"/>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
-      <c r="M20" s="26"/>
-      <c r="N20" s="27"/>
-    </row>
-    <row r="21" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="21">
+      <c r="M20" s="132"/>
+      <c r="N20" s="133"/>
+    </row>
+    <row r="21" spans="1:14" s="123" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="19">
         <v>9</v>
       </c>
-      <c r="B21" s="81" t="s">
+      <c r="B21" s="79" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="24"/>
-      <c r="D21" s="24"/>
-      <c r="E21" s="24"/>
-      <c r="F21" s="24"/>
-      <c r="G21" s="24"/>
-      <c r="H21" s="24"/>
-      <c r="I21" s="25"/>
+      <c r="C21" s="73"/>
+      <c r="D21" s="73"/>
+      <c r="E21" s="73"/>
+      <c r="F21" s="73"/>
+      <c r="G21" s="73"/>
+      <c r="H21" s="73"/>
+      <c r="I21" s="74"/>
       <c r="J21" s="4"/>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
-      <c r="M21" s="22"/>
-      <c r="N21" s="20"/>
+      <c r="M21" s="134"/>
+      <c r="N21" s="135"/>
     </row>
     <row r="22" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="77" t="s">
+      <c r="A22" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="B22" s="78"/>
-      <c r="C22" s="78"/>
-      <c r="D22" s="78"/>
-      <c r="E22" s="78"/>
-      <c r="F22" s="78"/>
-      <c r="G22" s="78"/>
-      <c r="H22" s="78"/>
-      <c r="I22" s="78"/>
-      <c r="J22" s="78"/>
-      <c r="K22" s="78"/>
-      <c r="L22" s="78"/>
-      <c r="M22" s="78"/>
-      <c r="N22" s="82"/>
-    </row>
-    <row r="23" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="24"/>
+      <c r="C22" s="24"/>
+      <c r="D22" s="24"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="24"/>
+      <c r="G22" s="24"/>
+      <c r="H22" s="24"/>
+      <c r="I22" s="24"/>
+      <c r="J22" s="24"/>
+      <c r="K22" s="24"/>
+      <c r="L22" s="24"/>
+      <c r="M22" s="24"/>
+      <c r="N22" s="25"/>
+    </row>
+    <row r="23" spans="1:14" s="123" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5">
         <v>10</v>
       </c>
-      <c r="B23" s="34" t="s">
+      <c r="B23" s="76" t="s">
         <v>29</v>
       </c>
-      <c r="C23" s="83"/>
-      <c r="D23" s="83"/>
-      <c r="E23" s="83"/>
-      <c r="F23" s="83"/>
-      <c r="G23" s="83"/>
-      <c r="H23" s="83"/>
-      <c r="I23" s="84"/>
+      <c r="C23" s="126"/>
+      <c r="D23" s="126"/>
+      <c r="E23" s="126"/>
+      <c r="F23" s="126"/>
+      <c r="G23" s="126"/>
+      <c r="H23" s="126"/>
+      <c r="I23" s="127"/>
       <c r="J23" s="6"/>
       <c r="K23" s="6"/>
       <c r="L23" s="6"/>
-      <c r="M23" s="26"/>
-      <c r="N23" s="27"/>
-    </row>
-    <row r="24" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M23" s="132"/>
+      <c r="N23" s="133"/>
+    </row>
+    <row r="24" spans="1:14" s="123" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5">
         <v>11</v>
       </c>
-      <c r="B24" s="34" t="s">
+      <c r="B24" s="76" t="s">
         <v>30</v>
       </c>
-      <c r="C24" s="83"/>
-      <c r="D24" s="83"/>
-      <c r="E24" s="83"/>
-      <c r="F24" s="83"/>
-      <c r="G24" s="83"/>
-      <c r="H24" s="83"/>
-      <c r="I24" s="84"/>
+      <c r="C24" s="126"/>
+      <c r="D24" s="126"/>
+      <c r="E24" s="126"/>
+      <c r="F24" s="126"/>
+      <c r="G24" s="126"/>
+      <c r="H24" s="126"/>
+      <c r="I24" s="127"/>
       <c r="J24" s="6"/>
       <c r="K24" s="6"/>
       <c r="L24" s="6"/>
-      <c r="M24" s="26"/>
-      <c r="N24" s="27"/>
-    </row>
-    <row r="25" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M24" s="132"/>
+      <c r="N24" s="133"/>
+    </row>
+    <row r="25" spans="1:14" s="123" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5">
         <v>12</v>
       </c>
-      <c r="B25" s="34" t="s">
+      <c r="B25" s="76" t="s">
         <v>81</v>
       </c>
-      <c r="C25" s="83"/>
-      <c r="D25" s="83"/>
-      <c r="E25" s="83"/>
-      <c r="F25" s="83"/>
-      <c r="G25" s="83"/>
-      <c r="H25" s="83"/>
-      <c r="I25" s="84"/>
+      <c r="C25" s="126"/>
+      <c r="D25" s="126"/>
+      <c r="E25" s="126"/>
+      <c r="F25" s="126"/>
+      <c r="G25" s="126"/>
+      <c r="H25" s="126"/>
+      <c r="I25" s="127"/>
       <c r="J25" s="6"/>
       <c r="K25" s="6"/>
       <c r="L25" s="6"/>
-      <c r="M25" s="26"/>
-      <c r="N25" s="27"/>
-    </row>
-    <row r="26" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M25" s="132"/>
+      <c r="N25" s="133"/>
+    </row>
+    <row r="26" spans="1:14" s="123" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="5">
         <v>13</v>
       </c>
-      <c r="B26" s="34" t="s">
+      <c r="B26" s="76" t="s">
         <v>82</v>
       </c>
-      <c r="C26" s="83"/>
-      <c r="D26" s="83"/>
-      <c r="E26" s="83"/>
-      <c r="F26" s="83"/>
-      <c r="G26" s="83"/>
-      <c r="H26" s="83"/>
-      <c r="I26" s="84"/>
+      <c r="C26" s="126"/>
+      <c r="D26" s="126"/>
+      <c r="E26" s="126"/>
+      <c r="F26" s="126"/>
+      <c r="G26" s="126"/>
+      <c r="H26" s="126"/>
+      <c r="I26" s="127"/>
       <c r="J26" s="6"/>
       <c r="K26" s="6"/>
       <c r="L26" s="6"/>
-      <c r="M26" s="26"/>
-      <c r="N26" s="27"/>
-    </row>
-    <row r="27" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M26" s="132"/>
+      <c r="N26" s="133"/>
+    </row>
+    <row r="27" spans="1:14" s="123" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="5">
         <v>14</v>
       </c>
-      <c r="B27" s="23" t="s">
+      <c r="B27" s="67" t="s">
         <v>31</v>
       </c>
-      <c r="C27" s="85"/>
-      <c r="D27" s="85"/>
-      <c r="E27" s="85"/>
-      <c r="F27" s="85"/>
-      <c r="G27" s="85"/>
-      <c r="H27" s="85"/>
-      <c r="I27" s="86"/>
+      <c r="C27" s="128"/>
+      <c r="D27" s="128"/>
+      <c r="E27" s="128"/>
+      <c r="F27" s="128"/>
+      <c r="G27" s="128"/>
+      <c r="H27" s="128"/>
+      <c r="I27" s="129"/>
       <c r="J27" s="6"/>
       <c r="K27" s="6"/>
       <c r="L27" s="6"/>
-      <c r="M27" s="26"/>
-      <c r="N27" s="27"/>
-    </row>
-    <row r="28" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M27" s="132"/>
+      <c r="N27" s="133"/>
+    </row>
+    <row r="28" spans="1:14" s="123" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="5">
         <v>15</v>
       </c>
-      <c r="B28" s="23" t="s">
+      <c r="B28" s="67" t="s">
         <v>98</v>
       </c>
-      <c r="C28" s="39"/>
-      <c r="D28" s="39"/>
-      <c r="E28" s="39"/>
-      <c r="F28" s="39"/>
-      <c r="G28" s="39"/>
-      <c r="H28" s="39"/>
-      <c r="I28" s="40"/>
+      <c r="C28" s="77"/>
+      <c r="D28" s="77"/>
+      <c r="E28" s="77"/>
+      <c r="F28" s="77"/>
+      <c r="G28" s="77"/>
+      <c r="H28" s="77"/>
+      <c r="I28" s="78"/>
       <c r="J28" s="6"/>
       <c r="K28" s="6"/>
       <c r="L28" s="6"/>
-      <c r="M28" s="19"/>
-      <c r="N28" s="20"/>
-    </row>
-    <row r="29" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M28" s="136"/>
+      <c r="N28" s="135"/>
+    </row>
+    <row r="29" spans="1:14" s="123" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="5">
         <v>16</v>
       </c>
-      <c r="B29" s="23" t="s">
+      <c r="B29" s="67" t="s">
         <v>32</v>
       </c>
-      <c r="C29" s="85"/>
-      <c r="D29" s="85"/>
-      <c r="E29" s="85"/>
-      <c r="F29" s="85"/>
-      <c r="G29" s="85"/>
-      <c r="H29" s="85"/>
-      <c r="I29" s="86"/>
+      <c r="C29" s="128"/>
+      <c r="D29" s="128"/>
+      <c r="E29" s="128"/>
+      <c r="F29" s="128"/>
+      <c r="G29" s="128"/>
+      <c r="H29" s="128"/>
+      <c r="I29" s="129"/>
       <c r="J29" s="4"/>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
-      <c r="M29" s="26"/>
-      <c r="N29" s="27"/>
-    </row>
-    <row r="30" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M29" s="132"/>
+      <c r="N29" s="133"/>
+    </row>
+    <row r="30" spans="1:14" s="123" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="5">
         <v>17</v>
       </c>
-      <c r="B30" s="23" t="s">
+      <c r="B30" s="67" t="s">
         <v>84</v>
       </c>
-      <c r="C30" s="85"/>
-      <c r="D30" s="85"/>
-      <c r="E30" s="85"/>
-      <c r="F30" s="85"/>
-      <c r="G30" s="85"/>
-      <c r="H30" s="85"/>
-      <c r="I30" s="86"/>
+      <c r="C30" s="128"/>
+      <c r="D30" s="128"/>
+      <c r="E30" s="128"/>
+      <c r="F30" s="128"/>
+      <c r="G30" s="128"/>
+      <c r="H30" s="128"/>
+      <c r="I30" s="129"/>
       <c r="J30" s="4"/>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
-      <c r="M30" s="26"/>
-      <c r="N30" s="27"/>
-    </row>
-    <row r="31" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M30" s="132"/>
+      <c r="N30" s="133"/>
+    </row>
+    <row r="31" spans="1:14" s="123" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="5">
         <v>18</v>
       </c>
-      <c r="B31" s="28" t="s">
+      <c r="B31" s="20" t="s">
         <v>97</v>
       </c>
-      <c r="C31" s="41"/>
-      <c r="D31" s="41"/>
-      <c r="E31" s="41"/>
-      <c r="F31" s="41"/>
-      <c r="G31" s="41"/>
-      <c r="H31" s="41"/>
-      <c r="I31" s="42"/>
+      <c r="C31" s="21"/>
+      <c r="D31" s="21"/>
+      <c r="E31" s="21"/>
+      <c r="F31" s="21"/>
+      <c r="G31" s="21"/>
+      <c r="H31" s="21"/>
+      <c r="I31" s="22"/>
       <c r="J31" s="6"/>
       <c r="K31" s="6"/>
       <c r="L31" s="6"/>
-      <c r="M31" s="136"/>
-      <c r="N31" s="137"/>
+      <c r="M31" s="137"/>
+      <c r="N31" s="138"/>
     </row>
     <row r="32" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="5">
         <v>19</v>
       </c>
-      <c r="B32" s="28" t="s">
+      <c r="B32" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="C32" s="29"/>
-      <c r="D32" s="29"/>
-      <c r="E32" s="29"/>
-      <c r="F32" s="29"/>
-      <c r="G32" s="29"/>
-      <c r="H32" s="29"/>
-      <c r="I32" s="30"/>
+      <c r="C32" s="121"/>
+      <c r="D32" s="121"/>
+      <c r="E32" s="121"/>
+      <c r="F32" s="121"/>
+      <c r="G32" s="121"/>
+      <c r="H32" s="121"/>
+      <c r="I32" s="122"/>
       <c r="J32" s="4"/>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
-      <c r="M32" s="26"/>
-      <c r="N32" s="27"/>
-    </row>
-    <row r="33" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M32" s="132"/>
+      <c r="N32" s="133"/>
+    </row>
+    <row r="33" spans="1:14" s="123" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="5">
         <v>20</v>
       </c>
-      <c r="B33" s="28" t="s">
+      <c r="B33" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="C33" s="41"/>
-      <c r="D33" s="41"/>
-      <c r="E33" s="41"/>
-      <c r="F33" s="41"/>
-      <c r="G33" s="41"/>
-      <c r="H33" s="41"/>
-      <c r="I33" s="42"/>
+      <c r="C33" s="21"/>
+      <c r="D33" s="21"/>
+      <c r="E33" s="21"/>
+      <c r="F33" s="21"/>
+      <c r="G33" s="21"/>
+      <c r="H33" s="21"/>
+      <c r="I33" s="22"/>
       <c r="J33" s="4"/>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
-      <c r="M33" s="26"/>
-      <c r="N33" s="27"/>
-    </row>
-    <row r="34" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M33" s="132"/>
+      <c r="N33" s="133"/>
+    </row>
+    <row r="34" spans="1:14" s="123" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="5">
         <v>21</v>
       </c>
-      <c r="B34" s="28" t="s">
+      <c r="B34" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="C34" s="29"/>
-      <c r="D34" s="29"/>
-      <c r="E34" s="29"/>
-      <c r="F34" s="29"/>
-      <c r="G34" s="29"/>
-      <c r="H34" s="29"/>
-      <c r="I34" s="30"/>
+      <c r="C34" s="121"/>
+      <c r="D34" s="121"/>
+      <c r="E34" s="121"/>
+      <c r="F34" s="121"/>
+      <c r="G34" s="121"/>
+      <c r="H34" s="121"/>
+      <c r="I34" s="122"/>
       <c r="J34" s="4"/>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
-      <c r="M34" s="26"/>
-      <c r="N34" s="27"/>
-    </row>
-    <row r="35" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M34" s="132"/>
+      <c r="N34" s="133"/>
+    </row>
+    <row r="35" spans="1:14" s="123" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="5">
         <v>22</v>
       </c>
-      <c r="B35" s="28" t="s">
+      <c r="B35" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="C35" s="29"/>
-      <c r="D35" s="29"/>
-      <c r="E35" s="29"/>
-      <c r="F35" s="29"/>
-      <c r="G35" s="29"/>
-      <c r="H35" s="29"/>
-      <c r="I35" s="30"/>
+      <c r="C35" s="121"/>
+      <c r="D35" s="121"/>
+      <c r="E35" s="121"/>
+      <c r="F35" s="121"/>
+      <c r="G35" s="121"/>
+      <c r="H35" s="121"/>
+      <c r="I35" s="122"/>
       <c r="J35" s="4"/>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
-      <c r="M35" s="26"/>
-      <c r="N35" s="27"/>
-    </row>
-    <row r="36" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M35" s="132"/>
+      <c r="N35" s="133"/>
+    </row>
+    <row r="36" spans="1:14" s="123" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="5">
         <v>23</v>
       </c>
-      <c r="B36" s="28" t="s">
+      <c r="B36" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="C36" s="29"/>
-      <c r="D36" s="29"/>
-      <c r="E36" s="29"/>
-      <c r="F36" s="29"/>
-      <c r="G36" s="29"/>
-      <c r="H36" s="29"/>
-      <c r="I36" s="30"/>
+      <c r="C36" s="121"/>
+      <c r="D36" s="121"/>
+      <c r="E36" s="121"/>
+      <c r="F36" s="121"/>
+      <c r="G36" s="121"/>
+      <c r="H36" s="121"/>
+      <c r="I36" s="122"/>
       <c r="J36" s="4"/>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
-      <c r="M36" s="26"/>
-      <c r="N36" s="27"/>
+      <c r="M36" s="132"/>
+      <c r="N36" s="133"/>
     </row>
     <row r="37" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="77" t="s">
+      <c r="A37" s="23" t="s">
         <v>70</v>
       </c>
-      <c r="B37" s="78"/>
-      <c r="C37" s="78"/>
-      <c r="D37" s="78"/>
-      <c r="E37" s="78"/>
-      <c r="F37" s="78"/>
-      <c r="G37" s="78"/>
-      <c r="H37" s="78"/>
-      <c r="I37" s="78"/>
-      <c r="J37" s="78"/>
-      <c r="K37" s="78"/>
-      <c r="L37" s="78"/>
-      <c r="M37" s="78"/>
-      <c r="N37" s="82"/>
-    </row>
-    <row r="38" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B37" s="24"/>
+      <c r="C37" s="24"/>
+      <c r="D37" s="24"/>
+      <c r="E37" s="24"/>
+      <c r="F37" s="24"/>
+      <c r="G37" s="24"/>
+      <c r="H37" s="24"/>
+      <c r="I37" s="24"/>
+      <c r="J37" s="24"/>
+      <c r="K37" s="24"/>
+      <c r="L37" s="24"/>
+      <c r="M37" s="24"/>
+      <c r="N37" s="25"/>
+    </row>
+    <row r="38" spans="1:14" s="123" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="3">
         <v>24</v>
       </c>
-      <c r="B38" s="28" t="s">
+      <c r="B38" s="20" t="s">
         <v>94</v>
       </c>
-      <c r="C38" s="41"/>
-      <c r="D38" s="41"/>
-      <c r="E38" s="41"/>
-      <c r="F38" s="41"/>
-      <c r="G38" s="41"/>
-      <c r="H38" s="41"/>
-      <c r="I38" s="42"/>
+      <c r="C38" s="21"/>
+      <c r="D38" s="21"/>
+      <c r="E38" s="21"/>
+      <c r="F38" s="21"/>
+      <c r="G38" s="21"/>
+      <c r="H38" s="21"/>
+      <c r="I38" s="22"/>
       <c r="J38" s="4"/>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
-      <c r="M38" s="26"/>
-      <c r="N38" s="27"/>
-    </row>
-    <row r="39" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="M38" s="132"/>
+      <c r="N38" s="133"/>
+    </row>
+    <row r="39" spans="1:14" s="123" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="3">
         <v>25</v>
       </c>
-      <c r="B39" s="31" t="s">
+      <c r="B39" s="116" t="s">
         <v>95</v>
       </c>
-      <c r="C39" s="32"/>
-      <c r="D39" s="32"/>
-      <c r="E39" s="32"/>
-      <c r="F39" s="32"/>
-      <c r="G39" s="32"/>
-      <c r="H39" s="32"/>
-      <c r="I39" s="33"/>
+      <c r="C39" s="117"/>
+      <c r="D39" s="117"/>
+      <c r="E39" s="117"/>
+      <c r="F39" s="117"/>
+      <c r="G39" s="117"/>
+      <c r="H39" s="117"/>
+      <c r="I39" s="118"/>
       <c r="J39" s="6"/>
       <c r="K39" s="6"/>
       <c r="L39" s="6"/>
-      <c r="M39" s="26"/>
-      <c r="N39" s="27"/>
-    </row>
-    <row r="40" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M39" s="132"/>
+      <c r="N39" s="133"/>
+    </row>
+    <row r="40" spans="1:14" s="123" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="3">
         <v>26</v>
       </c>
-      <c r="B40" s="34" t="s">
+      <c r="B40" s="76" t="s">
         <v>37</v>
       </c>
-      <c r="C40" s="35"/>
-      <c r="D40" s="35"/>
-      <c r="E40" s="35"/>
-      <c r="F40" s="35"/>
-      <c r="G40" s="35"/>
-      <c r="H40" s="35"/>
-      <c r="I40" s="36"/>
+      <c r="C40" s="119"/>
+      <c r="D40" s="119"/>
+      <c r="E40" s="119"/>
+      <c r="F40" s="119"/>
+      <c r="G40" s="119"/>
+      <c r="H40" s="119"/>
+      <c r="I40" s="120"/>
       <c r="J40" s="6"/>
       <c r="K40" s="6"/>
       <c r="L40" s="6"/>
-      <c r="M40" s="26"/>
-      <c r="N40" s="27"/>
+      <c r="M40" s="132"/>
+      <c r="N40" s="133"/>
     </row>
     <row r="41" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="89" t="s">
+      <c r="A41" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="B41" s="90"/>
-      <c r="C41" s="90"/>
-      <c r="D41" s="90"/>
-      <c r="E41" s="90"/>
-      <c r="F41" s="90"/>
-      <c r="G41" s="90"/>
-      <c r="H41" s="90"/>
-      <c r="I41" s="90"/>
-      <c r="J41" s="90"/>
-      <c r="K41" s="90"/>
-      <c r="L41" s="90"/>
-      <c r="M41" s="90"/>
-      <c r="N41" s="91"/>
-    </row>
-    <row r="42" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B41" s="27"/>
+      <c r="C41" s="27"/>
+      <c r="D41" s="27"/>
+      <c r="E41" s="27"/>
+      <c r="F41" s="27"/>
+      <c r="G41" s="27"/>
+      <c r="H41" s="27"/>
+      <c r="I41" s="27"/>
+      <c r="J41" s="27"/>
+      <c r="K41" s="27"/>
+      <c r="L41" s="27"/>
+      <c r="M41" s="27"/>
+      <c r="N41" s="28"/>
+    </row>
+    <row r="42" spans="1:14" s="123" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="3">
         <v>27</v>
       </c>
-      <c r="B42" s="23" t="s">
+      <c r="B42" s="67" t="s">
         <v>93</v>
       </c>
-      <c r="C42" s="39"/>
-      <c r="D42" s="39"/>
-      <c r="E42" s="39"/>
-      <c r="F42" s="39"/>
-      <c r="G42" s="39"/>
-      <c r="H42" s="39"/>
-      <c r="I42" s="40"/>
+      <c r="C42" s="77"/>
+      <c r="D42" s="77"/>
+      <c r="E42" s="77"/>
+      <c r="F42" s="77"/>
+      <c r="G42" s="77"/>
+      <c r="H42" s="77"/>
+      <c r="I42" s="78"/>
       <c r="J42" s="4"/>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
-      <c r="M42" s="26"/>
-      <c r="N42" s="27"/>
-    </row>
-    <row r="43" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M42" s="132"/>
+      <c r="N42" s="133"/>
+    </row>
+    <row r="43" spans="1:14" s="123" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="3">
         <v>28</v>
       </c>
-      <c r="B43" s="28" t="s">
+      <c r="B43" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="C43" s="41"/>
-      <c r="D43" s="41"/>
-      <c r="E43" s="41"/>
-      <c r="F43" s="41"/>
-      <c r="G43" s="41"/>
-      <c r="H43" s="41"/>
-      <c r="I43" s="42"/>
+      <c r="C43" s="21"/>
+      <c r="D43" s="21"/>
+      <c r="E43" s="21"/>
+      <c r="F43" s="21"/>
+      <c r="G43" s="21"/>
+      <c r="H43" s="21"/>
+      <c r="I43" s="22"/>
       <c r="J43" s="4"/>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
-      <c r="M43" s="26"/>
-      <c r="N43" s="27"/>
-    </row>
-    <row r="44" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M43" s="132"/>
+      <c r="N43" s="133"/>
+    </row>
+    <row r="44" spans="1:14" s="123" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="3">
         <v>29</v>
       </c>
-      <c r="B44" s="28" t="s">
+      <c r="B44" s="20" t="s">
         <v>99</v>
       </c>
-      <c r="C44" s="41"/>
-      <c r="D44" s="41"/>
-      <c r="E44" s="41"/>
-      <c r="F44" s="41"/>
-      <c r="G44" s="41"/>
-      <c r="H44" s="41"/>
-      <c r="I44" s="42"/>
+      <c r="C44" s="21"/>
+      <c r="D44" s="21"/>
+      <c r="E44" s="21"/>
+      <c r="F44" s="21"/>
+      <c r="G44" s="21"/>
+      <c r="H44" s="21"/>
+      <c r="I44" s="22"/>
       <c r="J44" s="4"/>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
-      <c r="M44" s="26"/>
-      <c r="N44" s="27"/>
-    </row>
-    <row r="45" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M44" s="132"/>
+      <c r="N44" s="133"/>
+    </row>
+    <row r="45" spans="1:14" s="123" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="3">
         <v>30</v>
       </c>
-      <c r="B45" s="28" t="s">
+      <c r="B45" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="C45" s="37"/>
-      <c r="D45" s="37"/>
-      <c r="E45" s="37"/>
-      <c r="F45" s="37"/>
-      <c r="G45" s="37"/>
-      <c r="H45" s="37"/>
-      <c r="I45" s="38"/>
+      <c r="C45" s="124"/>
+      <c r="D45" s="124"/>
+      <c r="E45" s="124"/>
+      <c r="F45" s="124"/>
+      <c r="G45" s="124"/>
+      <c r="H45" s="124"/>
+      <c r="I45" s="125"/>
       <c r="J45" s="4"/>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
-      <c r="M45" s="26"/>
-      <c r="N45" s="27"/>
-    </row>
-    <row r="46" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M45" s="132"/>
+      <c r="N45" s="133"/>
+    </row>
+    <row r="46" spans="1:14" s="123" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="3">
         <v>31</v>
       </c>
-      <c r="B46" s="28" t="s">
+      <c r="B46" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="C46" s="37"/>
-      <c r="D46" s="37"/>
-      <c r="E46" s="37"/>
-      <c r="F46" s="37"/>
-      <c r="G46" s="37"/>
-      <c r="H46" s="37"/>
-      <c r="I46" s="38"/>
+      <c r="C46" s="124"/>
+      <c r="D46" s="124"/>
+      <c r="E46" s="124"/>
+      <c r="F46" s="124"/>
+      <c r="G46" s="124"/>
+      <c r="H46" s="124"/>
+      <c r="I46" s="125"/>
       <c r="J46" s="4"/>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
-      <c r="M46" s="26"/>
-      <c r="N46" s="27"/>
+      <c r="M46" s="132"/>
+      <c r="N46" s="133"/>
     </row>
     <row r="47" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="89" t="s">
+      <c r="A47" s="26" t="s">
         <v>72</v>
       </c>
-      <c r="B47" s="90"/>
-      <c r="C47" s="90"/>
-      <c r="D47" s="90"/>
-      <c r="E47" s="90"/>
-      <c r="F47" s="90"/>
-      <c r="G47" s="90"/>
-      <c r="H47" s="90"/>
-      <c r="I47" s="90"/>
-      <c r="J47" s="90"/>
-      <c r="K47" s="90"/>
-      <c r="L47" s="90"/>
-      <c r="M47" s="90"/>
-      <c r="N47" s="91"/>
-    </row>
-    <row r="48" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B47" s="27"/>
+      <c r="C47" s="27"/>
+      <c r="D47" s="27"/>
+      <c r="E47" s="27"/>
+      <c r="F47" s="27"/>
+      <c r="G47" s="27"/>
+      <c r="H47" s="27"/>
+      <c r="I47" s="27"/>
+      <c r="J47" s="27"/>
+      <c r="K47" s="27"/>
+      <c r="L47" s="27"/>
+      <c r="M47" s="27"/>
+      <c r="N47" s="28"/>
+    </row>
+    <row r="48" spans="1:14" s="123" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="3">
         <v>32</v>
       </c>
-      <c r="B48" s="28" t="s">
+      <c r="B48" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="C48" s="37"/>
-      <c r="D48" s="37"/>
-      <c r="E48" s="37"/>
-      <c r="F48" s="37"/>
-      <c r="G48" s="37"/>
-      <c r="H48" s="37"/>
-      <c r="I48" s="38"/>
+      <c r="C48" s="124"/>
+      <c r="D48" s="124"/>
+      <c r="E48" s="124"/>
+      <c r="F48" s="124"/>
+      <c r="G48" s="124"/>
+      <c r="H48" s="124"/>
+      <c r="I48" s="125"/>
       <c r="J48" s="4"/>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
-      <c r="M48" s="26"/>
-      <c r="N48" s="27"/>
-    </row>
-    <row r="49" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M48" s="132"/>
+      <c r="N48" s="133"/>
+    </row>
+    <row r="49" spans="1:14" s="123" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="3">
         <v>33</v>
       </c>
-      <c r="B49" s="23" t="s">
+      <c r="B49" s="67" t="s">
         <v>89</v>
       </c>
-      <c r="C49" s="24"/>
-      <c r="D49" s="24"/>
-      <c r="E49" s="24"/>
-      <c r="F49" s="24"/>
-      <c r="G49" s="24"/>
-      <c r="H49" s="24"/>
-      <c r="I49" s="25"/>
+      <c r="C49" s="73"/>
+      <c r="D49" s="73"/>
+      <c r="E49" s="73"/>
+      <c r="F49" s="73"/>
+      <c r="G49" s="73"/>
+      <c r="H49" s="73"/>
+      <c r="I49" s="74"/>
       <c r="J49" s="4"/>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
-      <c r="M49" s="26"/>
-      <c r="N49" s="27"/>
-    </row>
-    <row r="50" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M49" s="132"/>
+      <c r="N49" s="133"/>
+    </row>
+    <row r="50" spans="1:14" s="123" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="3">
         <v>34</v>
       </c>
-      <c r="B50" s="28" t="s">
+      <c r="B50" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="C50" s="37"/>
-      <c r="D50" s="37"/>
-      <c r="E50" s="37"/>
-      <c r="F50" s="37"/>
-      <c r="G50" s="37"/>
-      <c r="H50" s="37"/>
-      <c r="I50" s="38"/>
+      <c r="C50" s="124"/>
+      <c r="D50" s="124"/>
+      <c r="E50" s="124"/>
+      <c r="F50" s="124"/>
+      <c r="G50" s="124"/>
+      <c r="H50" s="124"/>
+      <c r="I50" s="125"/>
       <c r="J50" s="4"/>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
-      <c r="M50" s="26"/>
-      <c r="N50" s="27"/>
-    </row>
-    <row r="51" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M50" s="132"/>
+      <c r="N50" s="133"/>
+    </row>
+    <row r="51" spans="1:14" s="123" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="3">
         <v>35</v>
       </c>
-      <c r="B51" s="23" t="s">
+      <c r="B51" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="C51" s="24"/>
-      <c r="D51" s="24"/>
-      <c r="E51" s="24"/>
-      <c r="F51" s="24"/>
-      <c r="G51" s="24"/>
-      <c r="H51" s="24"/>
-      <c r="I51" s="25"/>
+      <c r="C51" s="73"/>
+      <c r="D51" s="73"/>
+      <c r="E51" s="73"/>
+      <c r="F51" s="73"/>
+      <c r="G51" s="73"/>
+      <c r="H51" s="73"/>
+      <c r="I51" s="74"/>
       <c r="J51" s="4"/>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
-      <c r="M51" s="19"/>
-      <c r="N51" s="20"/>
-    </row>
-    <row r="52" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M51" s="136"/>
+      <c r="N51" s="135"/>
+    </row>
+    <row r="52" spans="1:14" s="123" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="3">
         <v>36</v>
       </c>
-      <c r="B52" s="23" t="s">
+      <c r="B52" s="67" t="s">
         <v>90</v>
       </c>
-      <c r="C52" s="24"/>
-      <c r="D52" s="24"/>
-      <c r="E52" s="24"/>
-      <c r="F52" s="24"/>
-      <c r="G52" s="24"/>
-      <c r="H52" s="24"/>
-      <c r="I52" s="25"/>
+      <c r="C52" s="73"/>
+      <c r="D52" s="73"/>
+      <c r="E52" s="73"/>
+      <c r="F52" s="73"/>
+      <c r="G52" s="73"/>
+      <c r="H52" s="73"/>
+      <c r="I52" s="74"/>
       <c r="J52" s="4"/>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
-      <c r="M52" s="26"/>
-      <c r="N52" s="27"/>
-    </row>
-    <row r="53" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M52" s="132"/>
+      <c r="N52" s="133"/>
+    </row>
+    <row r="53" spans="1:14" s="123" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="3">
         <v>37</v>
       </c>
-      <c r="B53" s="28" t="s">
+      <c r="B53" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="C53" s="37"/>
-      <c r="D53" s="37"/>
-      <c r="E53" s="37"/>
-      <c r="F53" s="37"/>
-      <c r="G53" s="37"/>
-      <c r="H53" s="37"/>
-      <c r="I53" s="38"/>
+      <c r="C53" s="124"/>
+      <c r="D53" s="124"/>
+      <c r="E53" s="124"/>
+      <c r="F53" s="124"/>
+      <c r="G53" s="124"/>
+      <c r="H53" s="124"/>
+      <c r="I53" s="125"/>
       <c r="J53" s="4"/>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
-      <c r="M53" s="26"/>
-      <c r="N53" s="27"/>
-    </row>
-    <row r="54" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M53" s="132"/>
+      <c r="N53" s="133"/>
+    </row>
+    <row r="54" spans="1:14" s="123" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="3">
         <v>38</v>
       </c>
-      <c r="B54" s="23" t="s">
+      <c r="B54" s="67" t="s">
         <v>43</v>
       </c>
-      <c r="C54" s="24"/>
-      <c r="D54" s="24"/>
-      <c r="E54" s="24"/>
-      <c r="F54" s="24"/>
-      <c r="G54" s="24"/>
-      <c r="H54" s="24"/>
-      <c r="I54" s="25"/>
+      <c r="C54" s="73"/>
+      <c r="D54" s="73"/>
+      <c r="E54" s="73"/>
+      <c r="F54" s="73"/>
+      <c r="G54" s="73"/>
+      <c r="H54" s="73"/>
+      <c r="I54" s="74"/>
       <c r="J54" s="4"/>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>
-      <c r="M54" s="26"/>
-      <c r="N54" s="27"/>
-    </row>
-    <row r="55" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M54" s="132"/>
+      <c r="N54" s="133"/>
+    </row>
+    <row r="55" spans="1:14" s="123" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="3">
         <v>39</v>
       </c>
-      <c r="B55" s="28" t="s">
+      <c r="B55" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="C55" s="37"/>
-      <c r="D55" s="37"/>
-      <c r="E55" s="37"/>
-      <c r="F55" s="37"/>
-      <c r="G55" s="37"/>
-      <c r="H55" s="37"/>
-      <c r="I55" s="38"/>
+      <c r="C55" s="124"/>
+      <c r="D55" s="124"/>
+      <c r="E55" s="124"/>
+      <c r="F55" s="124"/>
+      <c r="G55" s="124"/>
+      <c r="H55" s="124"/>
+      <c r="I55" s="125"/>
       <c r="J55" s="4"/>
       <c r="K55" s="4"/>
       <c r="L55" s="4"/>
-      <c r="M55" s="26"/>
-      <c r="N55" s="27"/>
-    </row>
-    <row r="56" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M55" s="132"/>
+      <c r="N55" s="133"/>
+    </row>
+    <row r="56" spans="1:14" s="123" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="3">
         <v>40</v>
       </c>
-      <c r="B56" s="28" t="s">
+      <c r="B56" s="20" t="s">
         <v>91</v>
       </c>
-      <c r="C56" s="37"/>
-      <c r="D56" s="37"/>
-      <c r="E56" s="37"/>
-      <c r="F56" s="37"/>
-      <c r="G56" s="37"/>
-      <c r="H56" s="37"/>
-      <c r="I56" s="38"/>
+      <c r="C56" s="124"/>
+      <c r="D56" s="124"/>
+      <c r="E56" s="124"/>
+      <c r="F56" s="124"/>
+      <c r="G56" s="124"/>
+      <c r="H56" s="124"/>
+      <c r="I56" s="125"/>
       <c r="J56" s="4"/>
       <c r="K56" s="4"/>
       <c r="L56" s="4"/>
-      <c r="M56" s="26"/>
-      <c r="N56" s="27"/>
-    </row>
-    <row r="57" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M56" s="132"/>
+      <c r="N56" s="133"/>
+    </row>
+    <row r="57" spans="1:14" s="123" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="3">
         <v>41</v>
       </c>
-      <c r="B57" s="23" t="s">
+      <c r="B57" s="67" t="s">
         <v>45</v>
       </c>
-      <c r="C57" s="24"/>
-      <c r="D57" s="24"/>
-      <c r="E57" s="24"/>
-      <c r="F57" s="24"/>
-      <c r="G57" s="24"/>
-      <c r="H57" s="24"/>
-      <c r="I57" s="25"/>
+      <c r="C57" s="73"/>
+      <c r="D57" s="73"/>
+      <c r="E57" s="73"/>
+      <c r="F57" s="73"/>
+      <c r="G57" s="73"/>
+      <c r="H57" s="73"/>
+      <c r="I57" s="74"/>
       <c r="J57" s="4"/>
       <c r="K57" s="4"/>
       <c r="L57" s="4"/>
-      <c r="M57" s="26"/>
-      <c r="N57" s="27"/>
+      <c r="M57" s="132"/>
+      <c r="N57" s="133"/>
     </row>
     <row r="58" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="3">
         <v>42</v>
       </c>
-      <c r="B58" s="23" t="s">
+      <c r="B58" s="67" t="s">
         <v>92</v>
       </c>
-      <c r="C58" s="24"/>
-      <c r="D58" s="24"/>
-      <c r="E58" s="24"/>
-      <c r="F58" s="24"/>
-      <c r="G58" s="24"/>
-      <c r="H58" s="24"/>
-      <c r="I58" s="25"/>
+      <c r="C58" s="68"/>
+      <c r="D58" s="68"/>
+      <c r="E58" s="68"/>
+      <c r="F58" s="68"/>
+      <c r="G58" s="68"/>
+      <c r="H58" s="68"/>
+      <c r="I58" s="69"/>
       <c r="J58" s="4"/>
       <c r="K58" s="4"/>
       <c r="L58" s="4"/>
-      <c r="M58" s="26"/>
-      <c r="N58" s="27"/>
+      <c r="M58" s="132"/>
+      <c r="N58" s="133"/>
     </row>
     <row r="59" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="89" t="s">
+      <c r="A59" s="26" t="s">
         <v>73</v>
       </c>
-      <c r="B59" s="90"/>
-      <c r="C59" s="90"/>
-      <c r="D59" s="90"/>
-      <c r="E59" s="90"/>
-      <c r="F59" s="90"/>
-      <c r="G59" s="90"/>
-      <c r="H59" s="90"/>
-      <c r="I59" s="90"/>
-      <c r="J59" s="90"/>
-      <c r="K59" s="90"/>
-      <c r="L59" s="90"/>
-      <c r="M59" s="90"/>
-      <c r="N59" s="91"/>
-    </row>
-    <row r="60" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B59" s="27"/>
+      <c r="C59" s="27"/>
+      <c r="D59" s="27"/>
+      <c r="E59" s="27"/>
+      <c r="F59" s="27"/>
+      <c r="G59" s="27"/>
+      <c r="H59" s="27"/>
+      <c r="I59" s="27"/>
+      <c r="J59" s="27"/>
+      <c r="K59" s="27"/>
+      <c r="L59" s="27"/>
+      <c r="M59" s="27"/>
+      <c r="N59" s="28"/>
+    </row>
+    <row r="60" spans="1:14" s="123" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="3">
         <v>43</v>
       </c>
-      <c r="B60" s="28" t="s">
+      <c r="B60" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="C60" s="24"/>
-      <c r="D60" s="24"/>
-      <c r="E60" s="24"/>
-      <c r="F60" s="24"/>
-      <c r="G60" s="24"/>
-      <c r="H60" s="24"/>
-      <c r="I60" s="25"/>
+      <c r="C60" s="73"/>
+      <c r="D60" s="73"/>
+      <c r="E60" s="73"/>
+      <c r="F60" s="73"/>
+      <c r="G60" s="73"/>
+      <c r="H60" s="73"/>
+      <c r="I60" s="74"/>
       <c r="J60" s="4"/>
       <c r="K60" s="4"/>
       <c r="L60" s="4"/>
-      <c r="M60" s="26"/>
-      <c r="N60" s="27"/>
-    </row>
-    <row r="61" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M60" s="132"/>
+      <c r="N60" s="133"/>
+    </row>
+    <row r="61" spans="1:14" s="123" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="2">
         <v>44</v>
       </c>
-      <c r="B61" s="28" t="s">
+      <c r="B61" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="C61" s="37"/>
-      <c r="D61" s="37"/>
-      <c r="E61" s="37"/>
-      <c r="F61" s="37"/>
-      <c r="G61" s="37"/>
-      <c r="H61" s="37"/>
-      <c r="I61" s="38"/>
+      <c r="C61" s="124"/>
+      <c r="D61" s="124"/>
+      <c r="E61" s="124"/>
+      <c r="F61" s="124"/>
+      <c r="G61" s="124"/>
+      <c r="H61" s="124"/>
+      <c r="I61" s="125"/>
       <c r="J61" s="4"/>
       <c r="K61" s="4"/>
       <c r="L61" s="4"/>
-      <c r="M61" s="26"/>
-      <c r="N61" s="27"/>
-    </row>
-    <row r="62" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M61" s="132"/>
+      <c r="N61" s="133"/>
+    </row>
+    <row r="62" spans="1:14" s="123" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="2">
         <v>45</v>
       </c>
-      <c r="B62" s="28" t="s">
+      <c r="B62" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="C62" s="37"/>
-      <c r="D62" s="37"/>
-      <c r="E62" s="37"/>
-      <c r="F62" s="37"/>
-      <c r="G62" s="37"/>
-      <c r="H62" s="37"/>
-      <c r="I62" s="38"/>
+      <c r="C62" s="124"/>
+      <c r="D62" s="124"/>
+      <c r="E62" s="124"/>
+      <c r="F62" s="124"/>
+      <c r="G62" s="124"/>
+      <c r="H62" s="124"/>
+      <c r="I62" s="125"/>
       <c r="J62" s="4"/>
       <c r="K62" s="4"/>
       <c r="L62" s="4"/>
-      <c r="M62" s="26"/>
-      <c r="N62" s="27"/>
-    </row>
-    <row r="63" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M62" s="132"/>
+      <c r="N62" s="133"/>
+    </row>
+    <row r="63" spans="1:14" s="123" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="2">
         <v>46</v>
       </c>
-      <c r="B63" s="23" t="s">
+      <c r="B63" s="67" t="s">
         <v>85</v>
       </c>
-      <c r="C63" s="24"/>
-      <c r="D63" s="24"/>
-      <c r="E63" s="24"/>
-      <c r="F63" s="24"/>
-      <c r="G63" s="24"/>
-      <c r="H63" s="24"/>
-      <c r="I63" s="25"/>
+      <c r="C63" s="73"/>
+      <c r="D63" s="73"/>
+      <c r="E63" s="73"/>
+      <c r="F63" s="73"/>
+      <c r="G63" s="73"/>
+      <c r="H63" s="73"/>
+      <c r="I63" s="74"/>
       <c r="J63" s="4"/>
       <c r="K63" s="4"/>
       <c r="L63" s="4"/>
-      <c r="M63" s="26"/>
-      <c r="N63" s="27"/>
+      <c r="M63" s="132"/>
+      <c r="N63" s="133"/>
     </row>
     <row r="64" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="77" t="s">
+      <c r="A64" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="B64" s="78"/>
-      <c r="C64" s="78"/>
-      <c r="D64" s="78"/>
-      <c r="E64" s="78"/>
-      <c r="F64" s="78"/>
-      <c r="G64" s="78"/>
-      <c r="H64" s="78"/>
-      <c r="I64" s="78"/>
-      <c r="J64" s="78"/>
-      <c r="K64" s="78"/>
-      <c r="L64" s="78"/>
-      <c r="M64" s="78"/>
-      <c r="N64" s="82"/>
-    </row>
-    <row r="65" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B64" s="24"/>
+      <c r="C64" s="24"/>
+      <c r="D64" s="24"/>
+      <c r="E64" s="24"/>
+      <c r="F64" s="24"/>
+      <c r="G64" s="24"/>
+      <c r="H64" s="24"/>
+      <c r="I64" s="24"/>
+      <c r="J64" s="24"/>
+      <c r="K64" s="24"/>
+      <c r="L64" s="24"/>
+      <c r="M64" s="24"/>
+      <c r="N64" s="25"/>
+    </row>
+    <row r="65" spans="1:14" s="123" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="5">
         <v>47</v>
       </c>
-      <c r="B65" s="34" t="s">
+      <c r="B65" s="76" t="s">
         <v>48</v>
       </c>
-      <c r="C65" s="87"/>
-      <c r="D65" s="87"/>
-      <c r="E65" s="87"/>
-      <c r="F65" s="87"/>
-      <c r="G65" s="87"/>
-      <c r="H65" s="87"/>
-      <c r="I65" s="88"/>
+      <c r="C65" s="130"/>
+      <c r="D65" s="130"/>
+      <c r="E65" s="130"/>
+      <c r="F65" s="130"/>
+      <c r="G65" s="130"/>
+      <c r="H65" s="130"/>
+      <c r="I65" s="131"/>
       <c r="J65" s="6"/>
       <c r="K65" s="6"/>
       <c r="L65" s="6"/>
-      <c r="M65" s="26"/>
-      <c r="N65" s="27"/>
-    </row>
-    <row r="66" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="M65" s="132"/>
+      <c r="N65" s="133"/>
+    </row>
+    <row r="66" spans="1:14" s="123" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="5">
         <v>48</v>
       </c>
-      <c r="B66" s="92" t="s">
+      <c r="B66" s="75" t="s">
         <v>49</v>
       </c>
-      <c r="C66" s="92"/>
-      <c r="D66" s="92"/>
-      <c r="E66" s="92"/>
-      <c r="F66" s="92"/>
-      <c r="G66" s="92"/>
-      <c r="H66" s="92"/>
-      <c r="I66" s="92"/>
+      <c r="C66" s="75"/>
+      <c r="D66" s="75"/>
+      <c r="E66" s="75"/>
+      <c r="F66" s="75"/>
+      <c r="G66" s="75"/>
+      <c r="H66" s="75"/>
+      <c r="I66" s="75"/>
       <c r="J66" s="4"/>
       <c r="K66" s="4"/>
       <c r="L66" s="4"/>
-      <c r="M66" s="26"/>
-      <c r="N66" s="27"/>
-    </row>
-    <row r="67" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M66" s="132"/>
+      <c r="N66" s="133"/>
+    </row>
+    <row r="67" spans="1:14" s="123" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="5">
         <v>49</v>
       </c>
-      <c r="B67" s="23" t="s">
+      <c r="B67" s="67" t="s">
         <v>50</v>
       </c>
-      <c r="C67" s="24"/>
-      <c r="D67" s="24"/>
-      <c r="E67" s="24"/>
-      <c r="F67" s="24"/>
-      <c r="G67" s="24"/>
-      <c r="H67" s="24"/>
-      <c r="I67" s="25"/>
+      <c r="C67" s="73"/>
+      <c r="D67" s="73"/>
+      <c r="E67" s="73"/>
+      <c r="F67" s="73"/>
+      <c r="G67" s="73"/>
+      <c r="H67" s="73"/>
+      <c r="I67" s="74"/>
       <c r="J67" s="4"/>
       <c r="K67" s="4"/>
       <c r="L67" s="4"/>
-      <c r="M67" s="26"/>
-      <c r="N67" s="27"/>
-    </row>
-    <row r="68" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="M67" s="132"/>
+      <c r="N67" s="133"/>
+    </row>
+    <row r="68" spans="1:14" s="123" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="5">
         <v>50</v>
       </c>
-      <c r="B68" s="92" t="s">
+      <c r="B68" s="75" t="s">
         <v>87</v>
       </c>
-      <c r="C68" s="92"/>
-      <c r="D68" s="92"/>
-      <c r="E68" s="92"/>
-      <c r="F68" s="92"/>
-      <c r="G68" s="92"/>
-      <c r="H68" s="92"/>
-      <c r="I68" s="92"/>
+      <c r="C68" s="75"/>
+      <c r="D68" s="75"/>
+      <c r="E68" s="75"/>
+      <c r="F68" s="75"/>
+      <c r="G68" s="75"/>
+      <c r="H68" s="75"/>
+      <c r="I68" s="75"/>
       <c r="J68" s="4"/>
       <c r="K68" s="4"/>
       <c r="L68" s="4"/>
-      <c r="M68" s="26"/>
-      <c r="N68" s="27"/>
+      <c r="M68" s="132"/>
+      <c r="N68" s="133"/>
     </row>
     <row r="69" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="77" t="s">
+      <c r="A69" s="23" t="s">
         <v>75</v>
       </c>
-      <c r="B69" s="78"/>
-      <c r="C69" s="78"/>
-      <c r="D69" s="78"/>
-      <c r="E69" s="78"/>
-      <c r="F69" s="78"/>
-      <c r="G69" s="78"/>
-      <c r="H69" s="78"/>
-      <c r="I69" s="78"/>
-      <c r="J69" s="78"/>
-      <c r="K69" s="78"/>
-      <c r="L69" s="78"/>
-      <c r="M69" s="78"/>
-      <c r="N69" s="82"/>
-    </row>
-    <row r="70" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B69" s="24"/>
+      <c r="C69" s="24"/>
+      <c r="D69" s="24"/>
+      <c r="E69" s="24"/>
+      <c r="F69" s="24"/>
+      <c r="G69" s="24"/>
+      <c r="H69" s="24"/>
+      <c r="I69" s="24"/>
+      <c r="J69" s="24"/>
+      <c r="K69" s="24"/>
+      <c r="L69" s="24"/>
+      <c r="M69" s="24"/>
+      <c r="N69" s="25"/>
+    </row>
+    <row r="70" spans="1:14" s="123" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="5">
         <v>51</v>
       </c>
-      <c r="B70" s="28" t="s">
+      <c r="B70" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="C70" s="37"/>
-      <c r="D70" s="37"/>
-      <c r="E70" s="37"/>
-      <c r="F70" s="37"/>
-      <c r="G70" s="37"/>
-      <c r="H70" s="37"/>
-      <c r="I70" s="38"/>
+      <c r="C70" s="124"/>
+      <c r="D70" s="124"/>
+      <c r="E70" s="124"/>
+      <c r="F70" s="124"/>
+      <c r="G70" s="124"/>
+      <c r="H70" s="124"/>
+      <c r="I70" s="125"/>
       <c r="J70" s="4"/>
       <c r="K70" s="4"/>
       <c r="L70" s="4"/>
-      <c r="M70" s="26"/>
-      <c r="N70" s="27"/>
-    </row>
-    <row r="71" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M70" s="132"/>
+      <c r="N70" s="133"/>
+    </row>
+    <row r="71" spans="1:14" s="123" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="5">
         <v>52</v>
       </c>
-      <c r="B71" s="28" t="s">
+      <c r="B71" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="C71" s="37"/>
-      <c r="D71" s="37"/>
-      <c r="E71" s="37"/>
-      <c r="F71" s="37"/>
-      <c r="G71" s="37"/>
-      <c r="H71" s="37"/>
-      <c r="I71" s="38"/>
+      <c r="C71" s="124"/>
+      <c r="D71" s="124"/>
+      <c r="E71" s="124"/>
+      <c r="F71" s="124"/>
+      <c r="G71" s="124"/>
+      <c r="H71" s="124"/>
+      <c r="I71" s="125"/>
       <c r="J71" s="4"/>
       <c r="K71" s="4"/>
       <c r="L71" s="4"/>
-      <c r="M71" s="26"/>
-      <c r="N71" s="27"/>
-    </row>
-    <row r="72" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M71" s="132"/>
+      <c r="N71" s="133"/>
+    </row>
+    <row r="72" spans="1:14" s="123" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="5">
         <v>53</v>
       </c>
-      <c r="B72" s="23" t="s">
+      <c r="B72" s="67" t="s">
         <v>69</v>
       </c>
-      <c r="C72" s="24"/>
-      <c r="D72" s="24"/>
-      <c r="E72" s="24"/>
-      <c r="F72" s="24"/>
-      <c r="G72" s="24"/>
-      <c r="H72" s="24"/>
-      <c r="I72" s="25"/>
+      <c r="C72" s="73"/>
+      <c r="D72" s="73"/>
+      <c r="E72" s="73"/>
+      <c r="F72" s="73"/>
+      <c r="G72" s="73"/>
+      <c r="H72" s="73"/>
+      <c r="I72" s="74"/>
       <c r="J72" s="4"/>
       <c r="K72" s="4"/>
       <c r="L72" s="4"/>
-      <c r="M72" s="26"/>
-      <c r="N72" s="27"/>
+      <c r="M72" s="132"/>
+      <c r="N72" s="133"/>
     </row>
     <row r="73" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="77" t="s">
+      <c r="A73" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="B73" s="78"/>
-      <c r="C73" s="78"/>
-      <c r="D73" s="78"/>
-      <c r="E73" s="78"/>
-      <c r="F73" s="78"/>
-      <c r="G73" s="78"/>
-      <c r="H73" s="78"/>
-      <c r="I73" s="78"/>
-      <c r="J73" s="78"/>
-      <c r="K73" s="78"/>
-      <c r="L73" s="78"/>
-      <c r="M73" s="78"/>
-      <c r="N73" s="82"/>
-    </row>
-    <row r="74" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B73" s="24"/>
+      <c r="C73" s="24"/>
+      <c r="D73" s="24"/>
+      <c r="E73" s="24"/>
+      <c r="F73" s="24"/>
+      <c r="G73" s="24"/>
+      <c r="H73" s="24"/>
+      <c r="I73" s="24"/>
+      <c r="J73" s="24"/>
+      <c r="K73" s="24"/>
+      <c r="L73" s="24"/>
+      <c r="M73" s="24"/>
+      <c r="N73" s="25"/>
+    </row>
+    <row r="74" spans="1:14" s="123" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="5">
         <v>54</v>
       </c>
-      <c r="B74" s="23" t="s">
+      <c r="B74" s="67" t="s">
         <v>53</v>
       </c>
-      <c r="C74" s="24"/>
-      <c r="D74" s="24"/>
-      <c r="E74" s="24"/>
-      <c r="F74" s="24"/>
-      <c r="G74" s="24"/>
-      <c r="H74" s="24"/>
-      <c r="I74" s="25"/>
+      <c r="C74" s="73"/>
+      <c r="D74" s="73"/>
+      <c r="E74" s="73"/>
+      <c r="F74" s="73"/>
+      <c r="G74" s="73"/>
+      <c r="H74" s="73"/>
+      <c r="I74" s="74"/>
       <c r="J74" s="4"/>
       <c r="K74" s="4"/>
       <c r="L74" s="4"/>
-      <c r="M74" s="26"/>
-      <c r="N74" s="27"/>
-    </row>
-    <row r="75" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M74" s="132"/>
+      <c r="N74" s="133"/>
+    </row>
+    <row r="75" spans="1:14" s="123" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="5">
         <v>55</v>
       </c>
-      <c r="B75" s="28" t="s">
+      <c r="B75" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="C75" s="37"/>
-      <c r="D75" s="37"/>
-      <c r="E75" s="37"/>
-      <c r="F75" s="37"/>
-      <c r="G75" s="37"/>
-      <c r="H75" s="37"/>
-      <c r="I75" s="38"/>
+      <c r="C75" s="124"/>
+      <c r="D75" s="124"/>
+      <c r="E75" s="124"/>
+      <c r="F75" s="124"/>
+      <c r="G75" s="124"/>
+      <c r="H75" s="124"/>
+      <c r="I75" s="125"/>
       <c r="J75" s="4"/>
       <c r="K75" s="4"/>
       <c r="L75" s="4"/>
-      <c r="M75" s="26"/>
-      <c r="N75" s="27"/>
-    </row>
-    <row r="76" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M75" s="132"/>
+      <c r="N75" s="133"/>
+    </row>
+    <row r="76" spans="1:14" s="123" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="5">
         <v>56</v>
       </c>
-      <c r="B76" s="23" t="s">
+      <c r="B76" s="67" t="s">
         <v>55</v>
       </c>
-      <c r="C76" s="93"/>
-      <c r="D76" s="93"/>
-      <c r="E76" s="93"/>
-      <c r="F76" s="93"/>
-      <c r="G76" s="93"/>
-      <c r="H76" s="93"/>
-      <c r="I76" s="94"/>
+      <c r="C76" s="73"/>
+      <c r="D76" s="73"/>
+      <c r="E76" s="73"/>
+      <c r="F76" s="73"/>
+      <c r="G76" s="73"/>
+      <c r="H76" s="73"/>
+      <c r="I76" s="74"/>
       <c r="J76" s="4"/>
       <c r="K76" s="4"/>
       <c r="L76" s="4"/>
-      <c r="M76" s="26"/>
-      <c r="N76" s="27"/>
-    </row>
-    <row r="77" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M76" s="132"/>
+      <c r="N76" s="133"/>
+    </row>
+    <row r="77" spans="1:14" s="123" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="5">
         <v>57</v>
       </c>
-      <c r="B77" s="28" t="s">
+      <c r="B77" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="C77" s="37"/>
-      <c r="D77" s="37"/>
-      <c r="E77" s="37"/>
-      <c r="F77" s="37"/>
-      <c r="G77" s="37"/>
-      <c r="H77" s="37"/>
-      <c r="I77" s="38"/>
+      <c r="C77" s="124"/>
+      <c r="D77" s="124"/>
+      <c r="E77" s="124"/>
+      <c r="F77" s="124"/>
+      <c r="G77" s="124"/>
+      <c r="H77" s="124"/>
+      <c r="I77" s="125"/>
       <c r="J77" s="4"/>
       <c r="K77" s="4"/>
       <c r="L77" s="4"/>
-      <c r="M77" s="26"/>
-      <c r="N77" s="27"/>
-    </row>
-    <row r="78" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M77" s="132"/>
+      <c r="N77" s="133"/>
+    </row>
+    <row r="78" spans="1:14" s="123" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="5">
         <v>58</v>
       </c>
-      <c r="B78" s="23" t="s">
+      <c r="B78" s="67" t="s">
         <v>57</v>
       </c>
-      <c r="C78" s="24"/>
-      <c r="D78" s="24"/>
-      <c r="E78" s="24"/>
-      <c r="F78" s="24"/>
-      <c r="G78" s="24"/>
-      <c r="H78" s="24"/>
-      <c r="I78" s="25"/>
+      <c r="C78" s="73"/>
+      <c r="D78" s="73"/>
+      <c r="E78" s="73"/>
+      <c r="F78" s="73"/>
+      <c r="G78" s="73"/>
+      <c r="H78" s="73"/>
+      <c r="I78" s="74"/>
       <c r="J78" s="4"/>
       <c r="K78" s="4"/>
       <c r="L78" s="4"/>
-      <c r="M78" s="26"/>
-      <c r="N78" s="27"/>
+      <c r="M78" s="132"/>
+      <c r="N78" s="133"/>
     </row>
     <row r="79" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="110" t="s">
+      <c r="A79" s="70" t="s">
         <v>58</v>
       </c>
-      <c r="B79" s="111"/>
-      <c r="C79" s="111"/>
-      <c r="D79" s="111"/>
-      <c r="E79" s="111"/>
-      <c r="F79" s="111"/>
-      <c r="G79" s="111"/>
-      <c r="H79" s="111"/>
-      <c r="I79" s="111"/>
-      <c r="J79" s="111"/>
-      <c r="K79" s="111"/>
-      <c r="L79" s="111"/>
-      <c r="M79" s="111"/>
-      <c r="N79" s="112"/>
+      <c r="B79" s="71"/>
+      <c r="C79" s="71"/>
+      <c r="D79" s="71"/>
+      <c r="E79" s="71"/>
+      <c r="F79" s="71"/>
+      <c r="G79" s="71"/>
+      <c r="H79" s="71"/>
+      <c r="I79" s="71"/>
+      <c r="J79" s="71"/>
+      <c r="K79" s="71"/>
+      <c r="L79" s="71"/>
+      <c r="M79" s="71"/>
+      <c r="N79" s="72"/>
     </row>
     <row r="80" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="95" t="s">
+      <c r="A80" s="58" t="s">
         <v>59</v>
       </c>
-      <c r="B80" s="96"/>
-      <c r="C80" s="96"/>
-      <c r="D80" s="96"/>
-      <c r="E80" s="96"/>
-      <c r="F80" s="96"/>
-      <c r="G80" s="96"/>
-      <c r="H80" s="96"/>
-      <c r="I80" s="96"/>
-      <c r="J80" s="96"/>
-      <c r="K80" s="96"/>
-      <c r="L80" s="96"/>
-      <c r="M80" s="96"/>
-      <c r="N80" s="97"/>
+      <c r="B80" s="59"/>
+      <c r="C80" s="59"/>
+      <c r="D80" s="59"/>
+      <c r="E80" s="59"/>
+      <c r="F80" s="59"/>
+      <c r="G80" s="59"/>
+      <c r="H80" s="59"/>
+      <c r="I80" s="59"/>
+      <c r="J80" s="59"/>
+      <c r="K80" s="59"/>
+      <c r="L80" s="59"/>
+      <c r="M80" s="59"/>
+      <c r="N80" s="60"/>
     </row>
     <row r="81" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="98" t="s">
+      <c r="A81" s="61" t="s">
         <v>60</v>
       </c>
-      <c r="B81" s="99"/>
-      <c r="C81" s="99"/>
-      <c r="D81" s="99"/>
-      <c r="E81" s="99"/>
-      <c r="F81" s="99"/>
-      <c r="G81" s="99"/>
-      <c r="H81" s="99"/>
-      <c r="I81" s="99"/>
-      <c r="J81" s="99"/>
-      <c r="K81" s="99"/>
-      <c r="L81" s="99"/>
-      <c r="M81" s="99"/>
-      <c r="N81" s="100"/>
+      <c r="B81" s="62"/>
+      <c r="C81" s="62"/>
+      <c r="D81" s="62"/>
+      <c r="E81" s="62"/>
+      <c r="F81" s="62"/>
+      <c r="G81" s="62"/>
+      <c r="H81" s="62"/>
+      <c r="I81" s="62"/>
+      <c r="J81" s="62"/>
+      <c r="K81" s="62"/>
+      <c r="L81" s="62"/>
+      <c r="M81" s="62"/>
+      <c r="N81" s="63"/>
     </row>
     <row r="82" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="101" t="s">
+      <c r="A82" s="64" t="s">
         <v>61</v>
       </c>
-      <c r="B82" s="102"/>
-      <c r="C82" s="102"/>
-      <c r="D82" s="102"/>
-      <c r="E82" s="102"/>
-      <c r="F82" s="102"/>
-      <c r="G82" s="102"/>
-      <c r="H82" s="102"/>
-      <c r="I82" s="102"/>
-      <c r="J82" s="102"/>
-      <c r="K82" s="102"/>
-      <c r="L82" s="102"/>
-      <c r="M82" s="102"/>
-      <c r="N82" s="103"/>
+      <c r="B82" s="65"/>
+      <c r="C82" s="65"/>
+      <c r="D82" s="65"/>
+      <c r="E82" s="65"/>
+      <c r="F82" s="65"/>
+      <c r="G82" s="65"/>
+      <c r="H82" s="65"/>
+      <c r="I82" s="65"/>
+      <c r="J82" s="65"/>
+      <c r="K82" s="65"/>
+      <c r="L82" s="65"/>
+      <c r="M82" s="65"/>
+      <c r="N82" s="66"/>
     </row>
     <row r="83" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="101"/>
-      <c r="B83" s="102"/>
-      <c r="C83" s="102"/>
-      <c r="D83" s="102"/>
-      <c r="E83" s="102"/>
-      <c r="F83" s="102"/>
-      <c r="G83" s="102"/>
-      <c r="H83" s="102"/>
-      <c r="I83" s="102"/>
-      <c r="J83" s="102"/>
-      <c r="K83" s="102"/>
-      <c r="L83" s="102"/>
-      <c r="M83" s="102"/>
-      <c r="N83" s="103"/>
+      <c r="A83" s="64"/>
+      <c r="B83" s="65"/>
+      <c r="C83" s="65"/>
+      <c r="D83" s="65"/>
+      <c r="E83" s="65"/>
+      <c r="F83" s="65"/>
+      <c r="G83" s="65"/>
+      <c r="H83" s="65"/>
+      <c r="I83" s="65"/>
+      <c r="J83" s="65"/>
+      <c r="K83" s="65"/>
+      <c r="L83" s="65"/>
+      <c r="M83" s="65"/>
+      <c r="N83" s="66"/>
     </row>
     <row r="84" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="104"/>
-      <c r="B84" s="105"/>
-      <c r="C84" s="105"/>
-      <c r="D84" s="105"/>
-      <c r="E84" s="105"/>
-      <c r="F84" s="105"/>
-      <c r="G84" s="105"/>
-      <c r="H84" s="105"/>
-      <c r="I84" s="105"/>
-      <c r="J84" s="105"/>
-      <c r="K84" s="105"/>
-      <c r="L84" s="105"/>
-      <c r="M84" s="105"/>
-      <c r="N84" s="106"/>
+      <c r="A84" s="52"/>
+      <c r="B84" s="53"/>
+      <c r="C84" s="53"/>
+      <c r="D84" s="53"/>
+      <c r="E84" s="53"/>
+      <c r="F84" s="53"/>
+      <c r="G84" s="53"/>
+      <c r="H84" s="53"/>
+      <c r="I84" s="53"/>
+      <c r="J84" s="53"/>
+      <c r="K84" s="53"/>
+      <c r="L84" s="53"/>
+      <c r="M84" s="53"/>
+      <c r="N84" s="54"/>
     </row>
     <row r="85" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="107"/>
-      <c r="B85" s="108"/>
-      <c r="C85" s="108"/>
-      <c r="D85" s="108"/>
-      <c r="E85" s="108"/>
-      <c r="F85" s="108"/>
-      <c r="G85" s="108"/>
-      <c r="H85" s="108"/>
-      <c r="I85" s="108"/>
-      <c r="J85" s="108"/>
-      <c r="K85" s="108"/>
-      <c r="L85" s="108"/>
-      <c r="M85" s="108"/>
-      <c r="N85" s="109"/>
+      <c r="A85" s="55"/>
+      <c r="B85" s="56"/>
+      <c r="C85" s="56"/>
+      <c r="D85" s="56"/>
+      <c r="E85" s="56"/>
+      <c r="F85" s="56"/>
+      <c r="G85" s="56"/>
+      <c r="H85" s="56"/>
+      <c r="I85" s="56"/>
+      <c r="J85" s="56"/>
+      <c r="K85" s="56"/>
+      <c r="L85" s="56"/>
+      <c r="M85" s="56"/>
+      <c r="N85" s="57"/>
     </row>
     <row r="86" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="104"/>
-      <c r="B86" s="105"/>
-      <c r="C86" s="105"/>
-      <c r="D86" s="105"/>
-      <c r="E86" s="105"/>
-      <c r="F86" s="105"/>
-      <c r="G86" s="105"/>
-      <c r="H86" s="105"/>
-      <c r="I86" s="105"/>
-      <c r="J86" s="105"/>
-      <c r="K86" s="105"/>
-      <c r="L86" s="105"/>
-      <c r="M86" s="105"/>
-      <c r="N86" s="106"/>
+      <c r="A86" s="52"/>
+      <c r="B86" s="53"/>
+      <c r="C86" s="53"/>
+      <c r="D86" s="53"/>
+      <c r="E86" s="53"/>
+      <c r="F86" s="53"/>
+      <c r="G86" s="53"/>
+      <c r="H86" s="53"/>
+      <c r="I86" s="53"/>
+      <c r="J86" s="53"/>
+      <c r="K86" s="53"/>
+      <c r="L86" s="53"/>
+      <c r="M86" s="53"/>
+      <c r="N86" s="54"/>
     </row>
     <row r="87" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="107"/>
-      <c r="B87" s="108"/>
-      <c r="C87" s="108"/>
-      <c r="D87" s="108"/>
-      <c r="E87" s="108"/>
-      <c r="F87" s="108"/>
-      <c r="G87" s="108"/>
-      <c r="H87" s="108"/>
-      <c r="I87" s="108"/>
-      <c r="J87" s="108"/>
-      <c r="K87" s="108"/>
-      <c r="L87" s="108"/>
-      <c r="M87" s="108"/>
-      <c r="N87" s="109"/>
+      <c r="A87" s="55"/>
+      <c r="B87" s="56"/>
+      <c r="C87" s="56"/>
+      <c r="D87" s="56"/>
+      <c r="E87" s="56"/>
+      <c r="F87" s="56"/>
+      <c r="G87" s="56"/>
+      <c r="H87" s="56"/>
+      <c r="I87" s="56"/>
+      <c r="J87" s="56"/>
+      <c r="K87" s="56"/>
+      <c r="L87" s="56"/>
+      <c r="M87" s="56"/>
+      <c r="N87" s="57"/>
     </row>
     <row r="88" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="104"/>
-      <c r="B88" s="105"/>
-      <c r="C88" s="105"/>
-      <c r="D88" s="105"/>
-      <c r="E88" s="105"/>
-      <c r="F88" s="105"/>
-      <c r="G88" s="105"/>
-      <c r="H88" s="105"/>
-      <c r="I88" s="105"/>
-      <c r="J88" s="105"/>
-      <c r="K88" s="105"/>
-      <c r="L88" s="105"/>
-      <c r="M88" s="105"/>
-      <c r="N88" s="106"/>
+      <c r="A88" s="52"/>
+      <c r="B88" s="53"/>
+      <c r="C88" s="53"/>
+      <c r="D88" s="53"/>
+      <c r="E88" s="53"/>
+      <c r="F88" s="53"/>
+      <c r="G88" s="53"/>
+      <c r="H88" s="53"/>
+      <c r="I88" s="53"/>
+      <c r="J88" s="53"/>
+      <c r="K88" s="53"/>
+      <c r="L88" s="53"/>
+      <c r="M88" s="53"/>
+      <c r="N88" s="54"/>
     </row>
     <row r="89" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="107"/>
-      <c r="B89" s="108"/>
-      <c r="C89" s="108"/>
-      <c r="D89" s="108"/>
-      <c r="E89" s="108"/>
-      <c r="F89" s="108"/>
-      <c r="G89" s="108"/>
-      <c r="H89" s="108"/>
-      <c r="I89" s="108"/>
-      <c r="J89" s="108"/>
-      <c r="K89" s="108"/>
-      <c r="L89" s="108"/>
-      <c r="M89" s="108"/>
-      <c r="N89" s="109"/>
+      <c r="A89" s="55"/>
+      <c r="B89" s="56"/>
+      <c r="C89" s="56"/>
+      <c r="D89" s="56"/>
+      <c r="E89" s="56"/>
+      <c r="F89" s="56"/>
+      <c r="G89" s="56"/>
+      <c r="H89" s="56"/>
+      <c r="I89" s="56"/>
+      <c r="J89" s="56"/>
+      <c r="K89" s="56"/>
+      <c r="L89" s="56"/>
+      <c r="M89" s="56"/>
+      <c r="N89" s="57"/>
     </row>
     <row r="90" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="104"/>
-      <c r="B90" s="105"/>
-      <c r="C90" s="105"/>
-      <c r="D90" s="105"/>
-      <c r="E90" s="105"/>
-      <c r="F90" s="105"/>
-      <c r="G90" s="105"/>
-      <c r="H90" s="105"/>
-      <c r="I90" s="105"/>
-      <c r="J90" s="105"/>
-      <c r="K90" s="105"/>
-      <c r="L90" s="105"/>
-      <c r="M90" s="105"/>
-      <c r="N90" s="106"/>
+      <c r="A90" s="52"/>
+      <c r="B90" s="53"/>
+      <c r="C90" s="53"/>
+      <c r="D90" s="53"/>
+      <c r="E90" s="53"/>
+      <c r="F90" s="53"/>
+      <c r="G90" s="53"/>
+      <c r="H90" s="53"/>
+      <c r="I90" s="53"/>
+      <c r="J90" s="53"/>
+      <c r="K90" s="53"/>
+      <c r="L90" s="53"/>
+      <c r="M90" s="53"/>
+      <c r="N90" s="54"/>
     </row>
     <row r="91" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="107"/>
-      <c r="B91" s="108"/>
-      <c r="C91" s="108"/>
-      <c r="D91" s="108"/>
-      <c r="E91" s="108"/>
-      <c r="F91" s="108"/>
-      <c r="G91" s="108"/>
-      <c r="H91" s="108"/>
-      <c r="I91" s="108"/>
-      <c r="J91" s="108"/>
-      <c r="K91" s="108"/>
-      <c r="L91" s="108"/>
-      <c r="M91" s="108"/>
-      <c r="N91" s="109"/>
+      <c r="A91" s="55"/>
+      <c r="B91" s="56"/>
+      <c r="C91" s="56"/>
+      <c r="D91" s="56"/>
+      <c r="E91" s="56"/>
+      <c r="F91" s="56"/>
+      <c r="G91" s="56"/>
+      <c r="H91" s="56"/>
+      <c r="I91" s="56"/>
+      <c r="J91" s="56"/>
+      <c r="K91" s="56"/>
+      <c r="L91" s="56"/>
+      <c r="M91" s="56"/>
+      <c r="N91" s="57"/>
     </row>
     <row r="92" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="104"/>
-      <c r="B92" s="105"/>
-      <c r="C92" s="105"/>
-      <c r="D92" s="105"/>
-      <c r="E92" s="105"/>
-      <c r="F92" s="105"/>
-      <c r="G92" s="105"/>
-      <c r="H92" s="105"/>
-      <c r="I92" s="105"/>
-      <c r="J92" s="105"/>
-      <c r="K92" s="105"/>
-      <c r="L92" s="105"/>
-      <c r="M92" s="105"/>
-      <c r="N92" s="106"/>
+      <c r="A92" s="52"/>
+      <c r="B92" s="53"/>
+      <c r="C92" s="53"/>
+      <c r="D92" s="53"/>
+      <c r="E92" s="53"/>
+      <c r="F92" s="53"/>
+      <c r="G92" s="53"/>
+      <c r="H92" s="53"/>
+      <c r="I92" s="53"/>
+      <c r="J92" s="53"/>
+      <c r="K92" s="53"/>
+      <c r="L92" s="53"/>
+      <c r="M92" s="53"/>
+      <c r="N92" s="54"/>
     </row>
     <row r="93" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="107"/>
-      <c r="B93" s="108"/>
-      <c r="C93" s="108"/>
-      <c r="D93" s="108"/>
-      <c r="E93" s="108"/>
-      <c r="F93" s="108"/>
-      <c r="G93" s="108"/>
-      <c r="H93" s="108"/>
-      <c r="I93" s="108"/>
-      <c r="J93" s="108"/>
-      <c r="K93" s="108"/>
-      <c r="L93" s="108"/>
-      <c r="M93" s="108"/>
-      <c r="N93" s="109"/>
+      <c r="A93" s="55"/>
+      <c r="B93" s="56"/>
+      <c r="C93" s="56"/>
+      <c r="D93" s="56"/>
+      <c r="E93" s="56"/>
+      <c r="F93" s="56"/>
+      <c r="G93" s="56"/>
+      <c r="H93" s="56"/>
+      <c r="I93" s="56"/>
+      <c r="J93" s="56"/>
+      <c r="K93" s="56"/>
+      <c r="L93" s="56"/>
+      <c r="M93" s="56"/>
+      <c r="N93" s="57"/>
     </row>
     <row r="94" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="104"/>
-      <c r="B94" s="105"/>
-      <c r="C94" s="105"/>
-      <c r="D94" s="105"/>
-      <c r="E94" s="105"/>
-      <c r="F94" s="105"/>
-      <c r="G94" s="105"/>
-      <c r="H94" s="105"/>
-      <c r="I94" s="105"/>
-      <c r="J94" s="105"/>
-      <c r="K94" s="105"/>
-      <c r="L94" s="105"/>
-      <c r="M94" s="105"/>
-      <c r="N94" s="106"/>
+      <c r="A94" s="52"/>
+      <c r="B94" s="53"/>
+      <c r="C94" s="53"/>
+      <c r="D94" s="53"/>
+      <c r="E94" s="53"/>
+      <c r="F94" s="53"/>
+      <c r="G94" s="53"/>
+      <c r="H94" s="53"/>
+      <c r="I94" s="53"/>
+      <c r="J94" s="53"/>
+      <c r="K94" s="53"/>
+      <c r="L94" s="53"/>
+      <c r="M94" s="53"/>
+      <c r="N94" s="54"/>
     </row>
     <row r="95" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="107"/>
-      <c r="B95" s="108"/>
-      <c r="C95" s="108"/>
-      <c r="D95" s="108"/>
-      <c r="E95" s="108"/>
-      <c r="F95" s="108"/>
-      <c r="G95" s="108"/>
-      <c r="H95" s="108"/>
-      <c r="I95" s="108"/>
-      <c r="J95" s="108"/>
-      <c r="K95" s="108"/>
-      <c r="L95" s="108"/>
-      <c r="M95" s="108"/>
-      <c r="N95" s="109"/>
+      <c r="A95" s="55"/>
+      <c r="B95" s="56"/>
+      <c r="C95" s="56"/>
+      <c r="D95" s="56"/>
+      <c r="E95" s="56"/>
+      <c r="F95" s="56"/>
+      <c r="G95" s="56"/>
+      <c r="H95" s="56"/>
+      <c r="I95" s="56"/>
+      <c r="J95" s="56"/>
+      <c r="K95" s="56"/>
+      <c r="L95" s="56"/>
+      <c r="M95" s="56"/>
+      <c r="N95" s="57"/>
     </row>
     <row r="96" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="104"/>
-      <c r="B96" s="105"/>
-      <c r="C96" s="105"/>
-      <c r="D96" s="105"/>
-      <c r="E96" s="105"/>
-      <c r="F96" s="105"/>
-      <c r="G96" s="105"/>
-      <c r="H96" s="105"/>
-      <c r="I96" s="105"/>
-      <c r="J96" s="105"/>
-      <c r="K96" s="105"/>
-      <c r="L96" s="105"/>
-      <c r="M96" s="105"/>
-      <c r="N96" s="106"/>
+      <c r="A96" s="52"/>
+      <c r="B96" s="53"/>
+      <c r="C96" s="53"/>
+      <c r="D96" s="53"/>
+      <c r="E96" s="53"/>
+      <c r="F96" s="53"/>
+      <c r="G96" s="53"/>
+      <c r="H96" s="53"/>
+      <c r="I96" s="53"/>
+      <c r="J96" s="53"/>
+      <c r="K96" s="53"/>
+      <c r="L96" s="53"/>
+      <c r="M96" s="53"/>
+      <c r="N96" s="54"/>
     </row>
     <row r="97" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="107"/>
-      <c r="B97" s="108"/>
-      <c r="C97" s="108"/>
-      <c r="D97" s="108"/>
-      <c r="E97" s="108"/>
-      <c r="F97" s="108"/>
-      <c r="G97" s="108"/>
-      <c r="H97" s="108"/>
-      <c r="I97" s="108"/>
-      <c r="J97" s="108"/>
-      <c r="K97" s="108"/>
-      <c r="L97" s="108"/>
-      <c r="M97" s="108"/>
-      <c r="N97" s="109"/>
+      <c r="A97" s="55"/>
+      <c r="B97" s="56"/>
+      <c r="C97" s="56"/>
+      <c r="D97" s="56"/>
+      <c r="E97" s="56"/>
+      <c r="F97" s="56"/>
+      <c r="G97" s="56"/>
+      <c r="H97" s="56"/>
+      <c r="I97" s="56"/>
+      <c r="J97" s="56"/>
+      <c r="K97" s="56"/>
+      <c r="L97" s="56"/>
+      <c r="M97" s="56"/>
+      <c r="N97" s="57"/>
     </row>
     <row r="98" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="104"/>
-      <c r="B98" s="105"/>
-      <c r="C98" s="105"/>
-      <c r="D98" s="105"/>
-      <c r="E98" s="105"/>
-      <c r="F98" s="105"/>
-      <c r="G98" s="105"/>
-      <c r="H98" s="105"/>
-      <c r="I98" s="105"/>
-      <c r="J98" s="105"/>
-      <c r="K98" s="105"/>
-      <c r="L98" s="105"/>
-      <c r="M98" s="105"/>
-      <c r="N98" s="106"/>
+      <c r="A98" s="52"/>
+      <c r="B98" s="53"/>
+      <c r="C98" s="53"/>
+      <c r="D98" s="53"/>
+      <c r="E98" s="53"/>
+      <c r="F98" s="53"/>
+      <c r="G98" s="53"/>
+      <c r="H98" s="53"/>
+      <c r="I98" s="53"/>
+      <c r="J98" s="53"/>
+      <c r="K98" s="53"/>
+      <c r="L98" s="53"/>
+      <c r="M98" s="53"/>
+      <c r="N98" s="54"/>
     </row>
     <row r="99" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="107"/>
-      <c r="B99" s="108"/>
-      <c r="C99" s="108"/>
-      <c r="D99" s="108"/>
-      <c r="E99" s="108"/>
-      <c r="F99" s="108"/>
-      <c r="G99" s="108"/>
-      <c r="H99" s="108"/>
-      <c r="I99" s="108"/>
-      <c r="J99" s="108"/>
-      <c r="K99" s="108"/>
-      <c r="L99" s="108"/>
-      <c r="M99" s="108"/>
-      <c r="N99" s="109"/>
+      <c r="A99" s="55"/>
+      <c r="B99" s="56"/>
+      <c r="C99" s="56"/>
+      <c r="D99" s="56"/>
+      <c r="E99" s="56"/>
+      <c r="F99" s="56"/>
+      <c r="G99" s="56"/>
+      <c r="H99" s="56"/>
+      <c r="I99" s="56"/>
+      <c r="J99" s="56"/>
+      <c r="K99" s="56"/>
+      <c r="L99" s="56"/>
+      <c r="M99" s="56"/>
+      <c r="N99" s="57"/>
     </row>
     <row r="100" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="104"/>
-      <c r="B100" s="105"/>
-      <c r="C100" s="105"/>
-      <c r="D100" s="105"/>
-      <c r="E100" s="105"/>
-      <c r="F100" s="105"/>
-      <c r="G100" s="105"/>
-      <c r="H100" s="105"/>
-      <c r="I100" s="105"/>
-      <c r="J100" s="105"/>
-      <c r="K100" s="105"/>
-      <c r="L100" s="105"/>
-      <c r="M100" s="105"/>
-      <c r="N100" s="106"/>
+      <c r="A100" s="52"/>
+      <c r="B100" s="53"/>
+      <c r="C100" s="53"/>
+      <c r="D100" s="53"/>
+      <c r="E100" s="53"/>
+      <c r="F100" s="53"/>
+      <c r="G100" s="53"/>
+      <c r="H100" s="53"/>
+      <c r="I100" s="53"/>
+      <c r="J100" s="53"/>
+      <c r="K100" s="53"/>
+      <c r="L100" s="53"/>
+      <c r="M100" s="53"/>
+      <c r="N100" s="54"/>
     </row>
     <row r="101" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="107"/>
-      <c r="B101" s="108"/>
-      <c r="C101" s="108"/>
-      <c r="D101" s="108"/>
-      <c r="E101" s="108"/>
-      <c r="F101" s="108"/>
-      <c r="G101" s="108"/>
-      <c r="H101" s="108"/>
-      <c r="I101" s="108"/>
-      <c r="J101" s="108"/>
-      <c r="K101" s="108"/>
-      <c r="L101" s="108"/>
-      <c r="M101" s="108"/>
-      <c r="N101" s="109"/>
+      <c r="A101" s="55"/>
+      <c r="B101" s="56"/>
+      <c r="C101" s="56"/>
+      <c r="D101" s="56"/>
+      <c r="E101" s="56"/>
+      <c r="F101" s="56"/>
+      <c r="G101" s="56"/>
+      <c r="H101" s="56"/>
+      <c r="I101" s="56"/>
+      <c r="J101" s="56"/>
+      <c r="K101" s="56"/>
+      <c r="L101" s="56"/>
+      <c r="M101" s="56"/>
+      <c r="N101" s="57"/>
     </row>
     <row r="102" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="14"/>
@@ -8644,136 +8655,163 @@
       <c r="N107" s="7"/>
     </row>
     <row r="108" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="113" t="s">
+      <c r="A108" s="29" t="s">
         <v>63</v>
       </c>
-      <c r="B108" s="114"/>
-      <c r="C108" s="114"/>
-      <c r="D108" s="114"/>
-      <c r="E108" s="114"/>
-      <c r="F108" s="115"/>
+      <c r="B108" s="30"/>
+      <c r="C108" s="30"/>
+      <c r="D108" s="30"/>
+      <c r="E108" s="30"/>
+      <c r="F108" s="31"/>
       <c r="G108" s="18" t="s">
         <v>64</v>
       </c>
       <c r="H108" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="I108" s="113" t="s">
+      <c r="I108" s="29" t="s">
         <v>66</v>
       </c>
-      <c r="J108" s="114"/>
-      <c r="K108" s="115"/>
-      <c r="L108" s="113" t="s">
+      <c r="J108" s="30"/>
+      <c r="K108" s="31"/>
+      <c r="L108" s="29" t="s">
         <v>67</v>
       </c>
-      <c r="M108" s="114"/>
-      <c r="N108" s="115"/>
+      <c r="M108" s="30"/>
+      <c r="N108" s="31"/>
     </row>
     <row r="109" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="116" t="s">
+      <c r="A109" s="32" t="s">
         <v>77</v>
       </c>
-      <c r="B109" s="117"/>
-      <c r="C109" s="117"/>
-      <c r="D109" s="117"/>
-      <c r="E109" s="117"/>
-      <c r="F109" s="118"/>
-      <c r="G109" s="122" t="s">
+      <c r="B109" s="33"/>
+      <c r="C109" s="33"/>
+      <c r="D109" s="33"/>
+      <c r="E109" s="33"/>
+      <c r="F109" s="34"/>
+      <c r="G109" s="38" t="s">
         <v>78</v>
       </c>
-      <c r="H109" s="118" t="s">
+      <c r="H109" s="34" t="s">
         <v>79</v>
       </c>
-      <c r="I109" s="124">
+      <c r="I109" s="40">
         <v>45840</v>
       </c>
-      <c r="J109" s="125"/>
-      <c r="K109" s="126"/>
-      <c r="L109" s="130" t="s">
+      <c r="J109" s="41"/>
+      <c r="K109" s="42"/>
+      <c r="L109" s="46" t="s">
         <v>68</v>
       </c>
-      <c r="M109" s="131"/>
-      <c r="N109" s="132"/>
+      <c r="M109" s="47"/>
+      <c r="N109" s="48"/>
     </row>
     <row r="110" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="119"/>
-      <c r="B110" s="120"/>
-      <c r="C110" s="120"/>
-      <c r="D110" s="120"/>
-      <c r="E110" s="120"/>
-      <c r="F110" s="121"/>
-      <c r="G110" s="123"/>
-      <c r="H110" s="121"/>
-      <c r="I110" s="127"/>
-      <c r="J110" s="128"/>
-      <c r="K110" s="129"/>
-      <c r="L110" s="133"/>
-      <c r="M110" s="134"/>
-      <c r="N110" s="135"/>
+      <c r="A110" s="35"/>
+      <c r="B110" s="36"/>
+      <c r="C110" s="36"/>
+      <c r="D110" s="36"/>
+      <c r="E110" s="36"/>
+      <c r="F110" s="37"/>
+      <c r="G110" s="39"/>
+      <c r="H110" s="37"/>
+      <c r="I110" s="43"/>
+      <c r="J110" s="44"/>
+      <c r="K110" s="45"/>
+      <c r="L110" s="49"/>
+      <c r="M110" s="50"/>
+      <c r="N110" s="51"/>
     </row>
   </sheetData>
   <mergeCells count="173">
-    <mergeCell ref="M31:N31"/>
-    <mergeCell ref="B31:I31"/>
-    <mergeCell ref="B44:I44"/>
-    <mergeCell ref="M44:N44"/>
-    <mergeCell ref="B34:I34"/>
-    <mergeCell ref="M34:N34"/>
-    <mergeCell ref="A37:N37"/>
-    <mergeCell ref="B38:I38"/>
-    <mergeCell ref="M38:N38"/>
-    <mergeCell ref="A41:N41"/>
-    <mergeCell ref="B32:I32"/>
-    <mergeCell ref="M32:N32"/>
-    <mergeCell ref="B33:I33"/>
-    <mergeCell ref="M33:N33"/>
-    <mergeCell ref="B35:I35"/>
-    <mergeCell ref="M35:N35"/>
-    <mergeCell ref="A108:F108"/>
-    <mergeCell ref="I108:K108"/>
-    <mergeCell ref="L108:N108"/>
-    <mergeCell ref="A109:F110"/>
-    <mergeCell ref="G109:G110"/>
-    <mergeCell ref="H109:H110"/>
-    <mergeCell ref="I109:K110"/>
-    <mergeCell ref="L109:N110"/>
-    <mergeCell ref="A90:N91"/>
-    <mergeCell ref="A92:N93"/>
-    <mergeCell ref="A94:N95"/>
-    <mergeCell ref="A96:N97"/>
-    <mergeCell ref="A98:N99"/>
-    <mergeCell ref="A100:N101"/>
-    <mergeCell ref="A80:N80"/>
-    <mergeCell ref="A81:N81"/>
-    <mergeCell ref="A82:N83"/>
-    <mergeCell ref="A84:N85"/>
-    <mergeCell ref="A86:N87"/>
-    <mergeCell ref="A88:N89"/>
-    <mergeCell ref="B77:I77"/>
-    <mergeCell ref="M77:N77"/>
-    <mergeCell ref="B78:I78"/>
-    <mergeCell ref="M78:N78"/>
-    <mergeCell ref="A79:N79"/>
-    <mergeCell ref="B75:I75"/>
-    <mergeCell ref="M75:N75"/>
-    <mergeCell ref="B76:I76"/>
-    <mergeCell ref="M76:N76"/>
-    <mergeCell ref="A69:N69"/>
-    <mergeCell ref="B70:I70"/>
-    <mergeCell ref="B71:I71"/>
-    <mergeCell ref="M71:N71"/>
-    <mergeCell ref="B72:I72"/>
-    <mergeCell ref="M72:N72"/>
-    <mergeCell ref="M70:N70"/>
-    <mergeCell ref="B66:I66"/>
-    <mergeCell ref="M66:N66"/>
-    <mergeCell ref="B67:I67"/>
-    <mergeCell ref="M67:N67"/>
-    <mergeCell ref="B68:I68"/>
-    <mergeCell ref="M68:N68"/>
-    <mergeCell ref="A73:N73"/>
-    <mergeCell ref="B74:I74"/>
-    <mergeCell ref="M74:N74"/>
+    <mergeCell ref="B63:I63"/>
+    <mergeCell ref="M63:N63"/>
+    <mergeCell ref="B36:I36"/>
+    <mergeCell ref="M36:N36"/>
+    <mergeCell ref="B39:I39"/>
+    <mergeCell ref="M39:N39"/>
+    <mergeCell ref="B40:I40"/>
+    <mergeCell ref="M40:N40"/>
+    <mergeCell ref="B54:I54"/>
+    <mergeCell ref="B55:I55"/>
+    <mergeCell ref="B56:I56"/>
+    <mergeCell ref="M52:N52"/>
+    <mergeCell ref="M53:N53"/>
+    <mergeCell ref="M54:N54"/>
+    <mergeCell ref="B48:I48"/>
+    <mergeCell ref="M48:N48"/>
+    <mergeCell ref="B49:I49"/>
+    <mergeCell ref="M49:N49"/>
+    <mergeCell ref="B61:I61"/>
+    <mergeCell ref="M61:N61"/>
+    <mergeCell ref="B42:I42"/>
+    <mergeCell ref="M42:N42"/>
+    <mergeCell ref="B43:I43"/>
+    <mergeCell ref="M43:N43"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="H2:K2"/>
+    <mergeCell ref="L2:N2"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="E3:H3"/>
+    <mergeCell ref="I3:N3"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="D1:L1"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="E6:H6"/>
+    <mergeCell ref="I6:N6"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="E8:H8"/>
+    <mergeCell ref="I8:N8"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="E4:H4"/>
+    <mergeCell ref="I4:N4"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="E5:H5"/>
+    <mergeCell ref="I5:N5"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="E7:H7"/>
+    <mergeCell ref="I7:N7"/>
+    <mergeCell ref="B13:I13"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="B14:I14"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="A9:N9"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="I10:N10"/>
+    <mergeCell ref="A11:I11"/>
+    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="A12:N12"/>
+    <mergeCell ref="B18:I18"/>
+    <mergeCell ref="M18:N18"/>
+    <mergeCell ref="A22:N22"/>
+    <mergeCell ref="B23:I23"/>
+    <mergeCell ref="M23:N23"/>
+    <mergeCell ref="B15:I15"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="B16:I16"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="B17:I17"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="B19:I19"/>
+    <mergeCell ref="M19:N19"/>
+    <mergeCell ref="B20:I20"/>
+    <mergeCell ref="M20:N20"/>
+    <mergeCell ref="B21:I21"/>
+    <mergeCell ref="B27:I27"/>
+    <mergeCell ref="M27:N27"/>
+    <mergeCell ref="B29:I29"/>
+    <mergeCell ref="M29:N29"/>
+    <mergeCell ref="B30:I30"/>
+    <mergeCell ref="M30:N30"/>
+    <mergeCell ref="B24:I24"/>
+    <mergeCell ref="M24:N24"/>
+    <mergeCell ref="B25:I25"/>
+    <mergeCell ref="M25:N25"/>
+    <mergeCell ref="B26:I26"/>
+    <mergeCell ref="M26:N26"/>
+    <mergeCell ref="B28:I28"/>
     <mergeCell ref="B65:I65"/>
     <mergeCell ref="M65:N65"/>
     <mergeCell ref="A64:N64"/>
@@ -8798,94 +8836,67 @@
     <mergeCell ref="M62:N62"/>
     <mergeCell ref="B57:I57"/>
     <mergeCell ref="M57:N57"/>
-    <mergeCell ref="B27:I27"/>
-    <mergeCell ref="M27:N27"/>
-    <mergeCell ref="B29:I29"/>
-    <mergeCell ref="M29:N29"/>
-    <mergeCell ref="B30:I30"/>
-    <mergeCell ref="M30:N30"/>
-    <mergeCell ref="B24:I24"/>
-    <mergeCell ref="M24:N24"/>
-    <mergeCell ref="B25:I25"/>
-    <mergeCell ref="M25:N25"/>
-    <mergeCell ref="B26:I26"/>
-    <mergeCell ref="M26:N26"/>
-    <mergeCell ref="B28:I28"/>
-    <mergeCell ref="B18:I18"/>
-    <mergeCell ref="M18:N18"/>
-    <mergeCell ref="A22:N22"/>
-    <mergeCell ref="B23:I23"/>
-    <mergeCell ref="M23:N23"/>
-    <mergeCell ref="B15:I15"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="B16:I16"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="B17:I17"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="B19:I19"/>
-    <mergeCell ref="M19:N19"/>
-    <mergeCell ref="B20:I20"/>
-    <mergeCell ref="M20:N20"/>
-    <mergeCell ref="B21:I21"/>
-    <mergeCell ref="B13:I13"/>
-    <mergeCell ref="M13:N13"/>
-    <mergeCell ref="B14:I14"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="A9:N9"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="I10:N10"/>
-    <mergeCell ref="A11:I11"/>
-    <mergeCell ref="M11:N11"/>
-    <mergeCell ref="A12:N12"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="E6:H6"/>
-    <mergeCell ref="I6:N6"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="E8:H8"/>
-    <mergeCell ref="I8:N8"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="E4:H4"/>
-    <mergeCell ref="I4:N4"/>
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="E5:H5"/>
-    <mergeCell ref="I5:N5"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="E7:H7"/>
-    <mergeCell ref="I7:N7"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="H2:K2"/>
-    <mergeCell ref="L2:N2"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="E3:H3"/>
-    <mergeCell ref="I3:N3"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="D1:L1"/>
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="B63:I63"/>
-    <mergeCell ref="M63:N63"/>
-    <mergeCell ref="B36:I36"/>
-    <mergeCell ref="M36:N36"/>
-    <mergeCell ref="B39:I39"/>
-    <mergeCell ref="M39:N39"/>
-    <mergeCell ref="B40:I40"/>
-    <mergeCell ref="M40:N40"/>
-    <mergeCell ref="B54:I54"/>
-    <mergeCell ref="B55:I55"/>
-    <mergeCell ref="B56:I56"/>
-    <mergeCell ref="M52:N52"/>
-    <mergeCell ref="M53:N53"/>
-    <mergeCell ref="M54:N54"/>
-    <mergeCell ref="B48:I48"/>
-    <mergeCell ref="M48:N48"/>
-    <mergeCell ref="B49:I49"/>
-    <mergeCell ref="M49:N49"/>
-    <mergeCell ref="B61:I61"/>
-    <mergeCell ref="M61:N61"/>
-    <mergeCell ref="B42:I42"/>
-    <mergeCell ref="M42:N42"/>
-    <mergeCell ref="B43:I43"/>
-    <mergeCell ref="M43:N43"/>
+    <mergeCell ref="B66:I66"/>
+    <mergeCell ref="M66:N66"/>
+    <mergeCell ref="B67:I67"/>
+    <mergeCell ref="M67:N67"/>
+    <mergeCell ref="B68:I68"/>
+    <mergeCell ref="M68:N68"/>
+    <mergeCell ref="A73:N73"/>
+    <mergeCell ref="B74:I74"/>
+    <mergeCell ref="M74:N74"/>
+    <mergeCell ref="B75:I75"/>
+    <mergeCell ref="M75:N75"/>
+    <mergeCell ref="B76:I76"/>
+    <mergeCell ref="M76:N76"/>
+    <mergeCell ref="A69:N69"/>
+    <mergeCell ref="B70:I70"/>
+    <mergeCell ref="B71:I71"/>
+    <mergeCell ref="M71:N71"/>
+    <mergeCell ref="B72:I72"/>
+    <mergeCell ref="M72:N72"/>
+    <mergeCell ref="M70:N70"/>
+    <mergeCell ref="A80:N80"/>
+    <mergeCell ref="A81:N81"/>
+    <mergeCell ref="A82:N83"/>
+    <mergeCell ref="A84:N85"/>
+    <mergeCell ref="A86:N87"/>
+    <mergeCell ref="A88:N89"/>
+    <mergeCell ref="B77:I77"/>
+    <mergeCell ref="M77:N77"/>
+    <mergeCell ref="B78:I78"/>
+    <mergeCell ref="M78:N78"/>
+    <mergeCell ref="A79:N79"/>
+    <mergeCell ref="A108:F108"/>
+    <mergeCell ref="I108:K108"/>
+    <mergeCell ref="L108:N108"/>
+    <mergeCell ref="A109:F110"/>
+    <mergeCell ref="G109:G110"/>
+    <mergeCell ref="H109:H110"/>
+    <mergeCell ref="I109:K110"/>
+    <mergeCell ref="L109:N110"/>
+    <mergeCell ref="A90:N91"/>
+    <mergeCell ref="A92:N93"/>
+    <mergeCell ref="A94:N95"/>
+    <mergeCell ref="A96:N97"/>
+    <mergeCell ref="A98:N99"/>
+    <mergeCell ref="A100:N101"/>
+    <mergeCell ref="M31:N31"/>
+    <mergeCell ref="B31:I31"/>
+    <mergeCell ref="B44:I44"/>
+    <mergeCell ref="M44:N44"/>
+    <mergeCell ref="B34:I34"/>
+    <mergeCell ref="M34:N34"/>
+    <mergeCell ref="A37:N37"/>
+    <mergeCell ref="B38:I38"/>
+    <mergeCell ref="M38:N38"/>
+    <mergeCell ref="A41:N41"/>
+    <mergeCell ref="B32:I32"/>
+    <mergeCell ref="M32:N32"/>
+    <mergeCell ref="B33:I33"/>
+    <mergeCell ref="M33:N33"/>
+    <mergeCell ref="B35:I35"/>
+    <mergeCell ref="M35:N35"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -8898,15 +8909,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="7b8015c9-aad1-4bac-8950-78e0ae91757b">
@@ -8915,6 +8917,15 @@
     <TaxCatchAll xmlns="05331b14-7a17-452c-bd43-8b05eb5f4a9a" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9147,14 +9158,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62C42109-56F7-43FD-901C-A96B81441D92}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EFAD5FF3-893E-4A64-99A8-4D3292D7020F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
@@ -9167,6 +9170,14 @@
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="7b8015c9-aad1-4bac-8950-78e0ae91757b"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62C42109-56F7-43FD-901C-A96B81441D92}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
